--- a/html/Sygehus-EPJ-systemer_excel.XLSX
+++ b/html/Sygehus-EPJ-systemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA9F9838-7453-4B5D-A2CA-DA182FD7BC88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E411AEDA-C0BE-4C77-ABBB-1B75BF2A6ECC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30855" yWindow="1950" windowWidth="21600" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 19-12-2025" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 29-01-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sygehus_EPJ_systemer">'Opdateret d. 19-12-2025'!$A$1:$F$104</definedName>
+    <definedName name="Sygehus_EPJ_systemer">'Opdateret d. 29-01-2026'!$A$1:$F$104</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Sygehus-EPJ-systemer_excel.XLSX
+++ b/html/Sygehus-EPJ-systemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E411AEDA-C0BE-4C77-ABBB-1B75BF2A6ECC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F185D3D0-F3AD-43F1-978F-C8C77929F9EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 29-01-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 02-02-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sygehus_EPJ_systemer">'Opdateret d. 29-01-2026'!$A$1:$F$104</definedName>
+    <definedName name="Sygehus_EPJ_systemer">'Opdateret d. 02-02-2026'!$A$1:$F$104</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Sygehus-EPJ-systemer_excel.XLSX
+++ b/html/Sygehus-EPJ-systemer_excel.XLSX
@@ -5,25 +5,25 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F185D3D0-F3AD-43F1-978F-C8C77929F9EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38FB7C93-83BD-4FA1-B17B-177917427688}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 02-02-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 20-02-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sygehus_EPJ_systemer">'Opdateret d. 02-02-2026'!$A$1:$F$104</definedName>
+    <definedName name="Sygehus_EPJ_systemer">'Opdateret d. 20-02-2026'!$A$1:$F$107</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="480" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="492" uniqueCount="157">
   <si>
     <t>Standard</t>
   </si>
@@ -61,6 +61,16 @@
     <t>BIN01 (B0131X)</t>
   </si>
   <si>
+    <t>CareCommunication</t>
+  </si>
+  <si>
+    <t>CareCommunication (5.0_x000D_
+5.0)</t>
+  </si>
+  <si>
+    <t>Tester</t>
+  </si>
+  <si>
     <t>Negativ VANS kvittering</t>
   </si>
   <si>
@@ -154,9 +164,6 @@
     <t>GGOP (GGOP100)</t>
   </si>
   <si>
-    <t>Tester</t>
-  </si>
-  <si>
     <t>Personal Data Card</t>
   </si>
   <si>
@@ -328,13 +335,13 @@
     <t>XRPT05 (XR0532M)</t>
   </si>
   <si>
+    <t>Sende</t>
+  </si>
+  <si>
     <t>Appointment Document</t>
   </si>
   <si>
     <t>APD-DK (2.0.1)</t>
-  </si>
-  <si>
-    <t>Sende</t>
   </si>
   <si>
     <t>DGOP</t>
@@ -829,10 +836,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F104"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:F107"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -852,7 +859,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -869,7 +876,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -883,7 +890,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -893,22 +900,16 @@
       <c r="C4" t="s">
         <v>8</v>
       </c>
-      <c r="D4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E4" t="s">
-        <v>9</v>
-      </c>
       <c r="F4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C5" t="s">
         <v>8</v>
@@ -923,12 +924,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C6" t="s">
         <v>8</v>
@@ -943,12 +944,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C7" t="s">
         <v>8</v>
@@ -956,27 +957,33 @@
       <c r="D7" t="s">
         <v>9</v>
       </c>
+      <c r="E7" t="s">
+        <v>9</v>
+      </c>
       <c r="F7" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B8" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C8" t="s">
         <v>8</v>
       </c>
-      <c r="E8" t="s">
+      <c r="D8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F8" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
         <v>21</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>22</v>
       </c>
       <c r="B9" t="s">
         <v>23</v>
@@ -984,64 +991,64 @@
       <c r="C9" t="s">
         <v>8</v>
       </c>
-      <c r="D9" t="s">
-        <v>9</v>
-      </c>
-      <c r="F9" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E9" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B10" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C10" t="s">
         <v>8</v>
       </c>
-      <c r="E10" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>25</v>
       </c>
       <c r="B11" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C11" t="s">
         <v>8</v>
       </c>
-      <c r="D11" t="s">
-        <v>9</v>
-      </c>
-      <c r="F11" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B12" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C12" t="s">
         <v>8</v>
       </c>
+      <c r="D12" t="s">
+        <v>9</v>
+      </c>
       <c r="F12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B13" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C13" t="s">
         <v>8</v>
@@ -1050,12 +1057,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B14" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C14" t="s">
         <v>8</v>
@@ -1064,12 +1071,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B15" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C15" t="s">
         <v>8</v>
@@ -1078,12 +1085,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B16" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C16" t="s">
         <v>8</v>
@@ -1092,26 +1099,26 @@
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B17" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C17" t="s">
         <v>8</v>
       </c>
-      <c r="D17" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F17" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B18" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C18" t="s">
         <v>8</v>
@@ -1119,16 +1126,13 @@
       <c r="D18" t="s">
         <v>9</v>
       </c>
-      <c r="F18" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B19" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C19" t="s">
         <v>8</v>
@@ -1136,14 +1140,11 @@
       <c r="D19" t="s">
         <v>9</v>
       </c>
-      <c r="E19" t="s">
-        <v>43</v>
-      </c>
       <c r="F19" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>44</v>
       </c>
@@ -1156,27 +1157,30 @@
       <c r="D20" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E20" t="s">
+        <v>14</v>
+      </c>
+      <c r="F20" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B21" t="s">
+        <v>47</v>
+      </c>
+      <c r="C21" t="s">
+        <v>8</v>
+      </c>
+      <c r="D21" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
         <v>46</v>
-      </c>
-      <c r="C21" t="s">
-        <v>8</v>
-      </c>
-      <c r="D21" t="s">
-        <v>9</v>
-      </c>
-      <c r="F21" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>47</v>
       </c>
       <c r="B22" t="s">
         <v>48</v>
@@ -1184,11 +1188,14 @@
       <c r="C22" t="s">
         <v>8</v>
       </c>
-      <c r="E22" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D22" t="s">
+        <v>9</v>
+      </c>
+      <c r="F22" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>49</v>
       </c>
@@ -1202,7 +1209,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>51</v>
       </c>
@@ -1216,7 +1223,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>53</v>
       </c>
@@ -1226,36 +1233,30 @@
       <c r="C25" t="s">
         <v>8</v>
       </c>
-      <c r="D25" t="s">
-        <v>9</v>
-      </c>
-      <c r="F25" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E25" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B26" t="s">
+        <v>56</v>
+      </c>
+      <c r="C26" t="s">
+        <v>8</v>
+      </c>
+      <c r="D26" t="s">
+        <v>9</v>
+      </c>
+      <c r="F26" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
         <v>55</v>
-      </c>
-      <c r="C26" t="s">
-        <v>8</v>
-      </c>
-      <c r="D26" t="s">
-        <v>21</v>
-      </c>
-      <c r="E26" t="s">
-        <v>21</v>
-      </c>
-      <c r="F26" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>56</v>
       </c>
       <c r="B27" t="s">
         <v>57</v>
@@ -1263,33 +1264,33 @@
       <c r="C27" t="s">
         <v>8</v>
       </c>
+      <c r="D27" t="s">
+        <v>24</v>
+      </c>
+      <c r="E27" t="s">
+        <v>24</v>
+      </c>
       <c r="F27" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B28" t="s">
+        <v>59</v>
+      </c>
+      <c r="C28" t="s">
+        <v>8</v>
+      </c>
+      <c r="F28" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
         <v>58</v>
-      </c>
-      <c r="C28" t="s">
-        <v>8</v>
-      </c>
-      <c r="D28" t="s">
-        <v>21</v>
-      </c>
-      <c r="E28" t="s">
-        <v>43</v>
-      </c>
-      <c r="F28" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>59</v>
       </c>
       <c r="B29" t="s">
         <v>60</v>
@@ -1298,13 +1299,16 @@
         <v>8</v>
       </c>
       <c r="D29" t="s">
-        <v>9</v>
+        <v>24</v>
+      </c>
+      <c r="E29" t="s">
+        <v>14</v>
       </c>
       <c r="F29" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>61</v>
       </c>
@@ -1314,11 +1318,14 @@
       <c r="C30" t="s">
         <v>8</v>
       </c>
+      <c r="D30" t="s">
+        <v>9</v>
+      </c>
       <c r="F30" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>63</v>
       </c>
@@ -1328,11 +1335,11 @@
       <c r="C31" t="s">
         <v>8</v>
       </c>
-      <c r="D31" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F31" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>65</v>
       </c>
@@ -1346,7 +1353,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>67</v>
       </c>
@@ -1360,7 +1367,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>69</v>
       </c>
@@ -1374,7 +1381,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>71</v>
       </c>
@@ -1388,7 +1395,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>73</v>
       </c>
@@ -1402,7 +1409,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>75</v>
       </c>
@@ -1416,7 +1423,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>77</v>
       </c>
@@ -1429,11 +1436,8 @@
       <c r="D38" t="s">
         <v>9</v>
       </c>
-      <c r="F38" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>79</v>
       </c>
@@ -1446,14 +1450,11 @@
       <c r="D39" t="s">
         <v>9</v>
       </c>
-      <c r="E39" t="s">
-        <v>9</v>
-      </c>
       <c r="F39" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>81</v>
       </c>
@@ -1463,11 +1464,17 @@
       <c r="C40" t="s">
         <v>8</v>
       </c>
+      <c r="D40" t="s">
+        <v>9</v>
+      </c>
+      <c r="E40" t="s">
+        <v>9</v>
+      </c>
       <c r="F40" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>83</v>
       </c>
@@ -1477,11 +1484,11 @@
       <c r="C41" t="s">
         <v>8</v>
       </c>
-      <c r="E41" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F41" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>85</v>
       </c>
@@ -1491,14 +1498,11 @@
       <c r="C42" t="s">
         <v>8</v>
       </c>
-      <c r="D42" t="s">
-        <v>9</v>
-      </c>
-      <c r="F42" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E42" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>87</v>
       </c>
@@ -1511,8 +1515,11 @@
       <c r="D43" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F43" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>89</v>
       </c>
@@ -1522,27 +1529,27 @@
       <c r="C44" t="s">
         <v>8</v>
       </c>
-      <c r="F44" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D44" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B45" t="s">
+        <v>92</v>
+      </c>
+      <c r="C45" t="s">
+        <v>8</v>
+      </c>
+      <c r="F45" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
         <v>91</v>
-      </c>
-      <c r="C45" t="s">
-        <v>8</v>
-      </c>
-      <c r="F45" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>92</v>
       </c>
       <c r="B46" t="s">
         <v>93</v>
@@ -1554,23 +1561,23 @@
         <v>9</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B47" t="s">
+        <v>95</v>
+      </c>
+      <c r="C47" t="s">
+        <v>8</v>
+      </c>
+      <c r="F47" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
         <v>94</v>
-      </c>
-      <c r="C47" t="s">
-        <v>8</v>
-      </c>
-      <c r="F47" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>95</v>
       </c>
       <c r="B48" t="s">
         <v>96</v>
@@ -1582,23 +1589,23 @@
         <v>9</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B49" t="s">
+        <v>98</v>
+      </c>
+      <c r="C49" t="s">
+        <v>8</v>
+      </c>
+      <c r="F49" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
         <v>97</v>
-      </c>
-      <c r="C49" t="s">
-        <v>8</v>
-      </c>
-      <c r="F49" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>98</v>
       </c>
       <c r="B50" t="s">
         <v>99</v>
@@ -1610,125 +1617,116 @@
         <v>9</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B51" t="s">
+        <v>101</v>
+      </c>
+      <c r="C51" t="s">
+        <v>8</v>
+      </c>
+      <c r="F51" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
         <v>100</v>
-      </c>
-      <c r="C51" t="s">
-        <v>8</v>
-      </c>
-      <c r="F51" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
-        <v>101</v>
       </c>
       <c r="B52" t="s">
         <v>102</v>
       </c>
       <c r="C52" t="s">
-        <v>103</v>
+        <v>8</v>
       </c>
       <c r="F52" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
+        <v>6</v>
+      </c>
+      <c r="B53" t="s">
+        <v>7</v>
+      </c>
+      <c r="C53" t="s">
+        <v>103</v>
+      </c>
+      <c r="F53" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>104</v>
+      </c>
+      <c r="B54" t="s">
+        <v>105</v>
+      </c>
+      <c r="C54" t="s">
+        <v>103</v>
+      </c>
+      <c r="F54" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
         <v>10</v>
       </c>
-      <c r="B53" t="s">
+      <c r="B55" t="s">
         <v>11</v>
       </c>
-      <c r="C53" t="s">
-        <v>103</v>
-      </c>
-      <c r="D53" t="s">
-        <v>9</v>
-      </c>
-      <c r="F53" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
+      <c r="C55" t="s">
+        <v>103</v>
+      </c>
+      <c r="D55" t="s">
+        <v>9</v>
+      </c>
+      <c r="F55" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>12</v>
+      </c>
+      <c r="B56" t="s">
+        <v>13</v>
+      </c>
+      <c r="C56" t="s">
+        <v>103</v>
+      </c>
+      <c r="F56" t="s">
         <v>14</v>
       </c>
-      <c r="B54" t="s">
-        <v>15</v>
-      </c>
-      <c r="C54" t="s">
-        <v>103</v>
-      </c>
-      <c r="D54" t="s">
-        <v>9</v>
-      </c>
-      <c r="E54" t="s">
-        <v>9</v>
-      </c>
-      <c r="F54" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
-        <v>16</v>
-      </c>
-      <c r="B55" t="s">
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
         <v>17</v>
       </c>
-      <c r="C55" t="s">
-        <v>103</v>
-      </c>
-      <c r="D55" t="s">
-        <v>9</v>
-      </c>
-      <c r="E55" t="s">
-        <v>9</v>
-      </c>
-      <c r="F55" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
-        <v>104</v>
-      </c>
-      <c r="B56" t="s">
-        <v>105</v>
-      </c>
-      <c r="C56" t="s">
-        <v>103</v>
-      </c>
-      <c r="D56" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
+      <c r="B57" t="s">
         <v>18</v>
       </c>
-      <c r="B57" t="s">
+      <c r="C57" t="s">
+        <v>103</v>
+      </c>
+      <c r="D57" t="s">
+        <v>9</v>
+      </c>
+      <c r="E57" t="s">
+        <v>9</v>
+      </c>
+      <c r="F57" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
         <v>19</v>
-      </c>
-      <c r="C57" t="s">
-        <v>103</v>
-      </c>
-      <c r="D57" t="s">
-        <v>9</v>
-      </c>
-      <c r="F57" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
-        <v>18</v>
       </c>
       <c r="B58" t="s">
         <v>20</v>
@@ -1736,178 +1734,169 @@
       <c r="C58" t="s">
         <v>103</v>
       </c>
+      <c r="D58" t="s">
+        <v>9</v>
+      </c>
       <c r="E58" t="s">
+        <v>9</v>
+      </c>
+      <c r="F58" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>106</v>
+      </c>
+      <c r="B59" t="s">
+        <v>107</v>
+      </c>
+      <c r="C59" t="s">
+        <v>103</v>
+      </c>
+      <c r="D59" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
+      <c r="B60" t="s">
         <v>22</v>
       </c>
-      <c r="B59" t="s">
+      <c r="C60" t="s">
+        <v>103</v>
+      </c>
+      <c r="D60" t="s">
+        <v>9</v>
+      </c>
+      <c r="F60" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
+        <v>21</v>
+      </c>
+      <c r="B61" t="s">
         <v>23</v>
       </c>
-      <c r="C59" t="s">
-        <v>103</v>
-      </c>
-      <c r="D59" t="s">
-        <v>9</v>
-      </c>
-      <c r="F59" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
-        <v>22</v>
-      </c>
-      <c r="B60" t="s">
+      <c r="C61" t="s">
+        <v>103</v>
+      </c>
+      <c r="E61" t="s">
         <v>24</v>
       </c>
-      <c r="C60" t="s">
-        <v>103</v>
-      </c>
-      <c r="E60" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
         <v>25</v>
       </c>
-      <c r="B61" t="s">
+      <c r="B62" t="s">
         <v>26</v>
       </c>
-      <c r="C61" t="s">
-        <v>103</v>
-      </c>
-      <c r="D61" t="s">
-        <v>9</v>
-      </c>
-      <c r="F61" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
+      <c r="C62" t="s">
+        <v>103</v>
+      </c>
+      <c r="D62" t="s">
+        <v>9</v>
+      </c>
+      <c r="F62" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
+        <v>25</v>
+      </c>
+      <c r="B63" t="s">
         <v>27</v>
       </c>
-      <c r="B62" t="s">
+      <c r="C63" t="s">
+        <v>103</v>
+      </c>
+      <c r="E63" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
         <v>28</v>
       </c>
-      <c r="C62" t="s">
-        <v>103</v>
-      </c>
-      <c r="F62" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
-        <v>33</v>
-      </c>
-      <c r="B63" t="s">
-        <v>34</v>
-      </c>
-      <c r="C63" t="s">
-        <v>103</v>
-      </c>
-      <c r="F63" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
-        <v>35</v>
-      </c>
       <c r="B64" t="s">
+        <v>29</v>
+      </c>
+      <c r="C64" t="s">
+        <v>103</v>
+      </c>
+      <c r="D64" t="s">
+        <v>9</v>
+      </c>
+      <c r="F64" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>30</v>
+      </c>
+      <c r="B65" t="s">
+        <v>31</v>
+      </c>
+      <c r="C65" t="s">
+        <v>103</v>
+      </c>
+      <c r="F65" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
         <v>36</v>
       </c>
-      <c r="C64" t="s">
-        <v>103</v>
-      </c>
-      <c r="F64" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A65" t="s">
-        <v>106</v>
-      </c>
-      <c r="B65" t="s">
-        <v>107</v>
-      </c>
-      <c r="C65" t="s">
-        <v>103</v>
-      </c>
-      <c r="D65" t="s">
-        <v>9</v>
-      </c>
-      <c r="F65" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A66" t="s">
+      <c r="B66" t="s">
+        <v>37</v>
+      </c>
+      <c r="C66" t="s">
+        <v>103</v>
+      </c>
+      <c r="F66" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
+        <v>38</v>
+      </c>
+      <c r="B67" t="s">
+        <v>39</v>
+      </c>
+      <c r="C67" t="s">
+        <v>103</v>
+      </c>
+      <c r="F67" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
         <v>108</v>
       </c>
-      <c r="B66" t="s">
+      <c r="B68" t="s">
         <v>109</v>
       </c>
-      <c r="C66" t="s">
-        <v>103</v>
-      </c>
-      <c r="D66" t="s">
-        <v>9</v>
-      </c>
-      <c r="E66" t="s">
-        <v>9</v>
-      </c>
-      <c r="F66" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A67" t="s">
-        <v>39</v>
-      </c>
-      <c r="B67" t="s">
-        <v>40</v>
-      </c>
-      <c r="C67" t="s">
-        <v>103</v>
-      </c>
-      <c r="D67" t="s">
-        <v>9</v>
-      </c>
-      <c r="E67" t="s">
-        <v>9</v>
-      </c>
-      <c r="F67" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A68" t="s">
-        <v>41</v>
-      </c>
-      <c r="B68" t="s">
-        <v>42</v>
-      </c>
       <c r="C68" t="s">
         <v>103</v>
       </c>
       <c r="D68" t="s">
         <v>9</v>
       </c>
-      <c r="E68" t="s">
-        <v>9</v>
-      </c>
       <c r="F68" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>110</v>
       </c>
@@ -1920,480 +1909,492 @@
       <c r="D69" t="s">
         <v>9</v>
       </c>
+      <c r="E69" t="s">
+        <v>9</v>
+      </c>
       <c r="F69" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
+        <v>42</v>
+      </c>
+      <c r="B70" t="s">
+        <v>43</v>
+      </c>
+      <c r="C70" t="s">
+        <v>103</v>
+      </c>
+      <c r="D70" t="s">
+        <v>9</v>
+      </c>
+      <c r="E70" t="s">
+        <v>9</v>
+      </c>
+      <c r="F70" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>44</v>
+      </c>
+      <c r="B71" t="s">
+        <v>45</v>
+      </c>
+      <c r="C71" t="s">
+        <v>103</v>
+      </c>
+      <c r="D71" t="s">
+        <v>9</v>
+      </c>
+      <c r="E71" t="s">
+        <v>9</v>
+      </c>
+      <c r="F71" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
         <v>112</v>
       </c>
-      <c r="B70" t="s">
+      <c r="B72" t="s">
         <v>113</v>
       </c>
-      <c r="C70" t="s">
-        <v>103</v>
-      </c>
-      <c r="F70" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A71" t="s">
+      <c r="C72" t="s">
+        <v>103</v>
+      </c>
+      <c r="D72" t="s">
+        <v>9</v>
+      </c>
+      <c r="F72" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
         <v>114</v>
       </c>
-      <c r="B71" t="s">
+      <c r="B73" t="s">
         <v>115</v>
       </c>
-      <c r="C71" t="s">
-        <v>103</v>
-      </c>
-      <c r="D71" t="s">
-        <v>9</v>
-      </c>
-      <c r="F71" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A72" t="s">
+      <c r="C73" t="s">
+        <v>103</v>
+      </c>
+      <c r="F73" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
         <v>116</v>
       </c>
-      <c r="B72" t="s">
+      <c r="B74" t="s">
         <v>117</v>
       </c>
-      <c r="C72" t="s">
-        <v>103</v>
-      </c>
-      <c r="D72" t="s">
-        <v>9</v>
-      </c>
-      <c r="F72" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A73" t="s">
-        <v>51</v>
-      </c>
-      <c r="B73" t="s">
+      <c r="C74" t="s">
+        <v>103</v>
+      </c>
+      <c r="D74" t="s">
+        <v>9</v>
+      </c>
+      <c r="F74" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
         <v>118</v>
       </c>
-      <c r="C73" t="s">
-        <v>103</v>
-      </c>
-      <c r="F73" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A74" t="s">
+      <c r="B75" t="s">
+        <v>119</v>
+      </c>
+      <c r="C75" t="s">
+        <v>103</v>
+      </c>
+      <c r="D75" t="s">
+        <v>9</v>
+      </c>
+      <c r="F75" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
         <v>53</v>
       </c>
-      <c r="B74" t="s">
-        <v>54</v>
-      </c>
-      <c r="C74" t="s">
-        <v>103</v>
-      </c>
-      <c r="D74" t="s">
-        <v>9</v>
-      </c>
-      <c r="F74" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A75" t="s">
-        <v>53</v>
-      </c>
-      <c r="B75" t="s">
+      <c r="B76" t="s">
+        <v>120</v>
+      </c>
+      <c r="C76" t="s">
+        <v>103</v>
+      </c>
+      <c r="F76" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
         <v>55</v>
       </c>
-      <c r="C75" t="s">
-        <v>103</v>
-      </c>
-      <c r="D75" t="s">
-        <v>21</v>
-      </c>
-      <c r="E75" t="s">
-        <v>21</v>
-      </c>
-      <c r="F75" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A76" t="s">
+      <c r="B77" t="s">
         <v>56</v>
       </c>
-      <c r="B76" t="s">
+      <c r="C77" t="s">
+        <v>103</v>
+      </c>
+      <c r="D77" t="s">
+        <v>9</v>
+      </c>
+      <c r="F77" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>55</v>
+      </c>
+      <c r="B78" t="s">
         <v>57</v>
       </c>
-      <c r="C76" t="s">
-        <v>103</v>
-      </c>
-      <c r="F76" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A77" t="s">
-        <v>56</v>
-      </c>
-      <c r="B77" t="s">
+      <c r="C78" t="s">
+        <v>103</v>
+      </c>
+      <c r="D78" t="s">
+        <v>24</v>
+      </c>
+      <c r="E78" t="s">
+        <v>24</v>
+      </c>
+      <c r="F78" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
         <v>58</v>
       </c>
-      <c r="C77" t="s">
-        <v>103</v>
-      </c>
-      <c r="E77" t="s">
-        <v>43</v>
-      </c>
-      <c r="F77" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A78" t="s">
-        <v>119</v>
-      </c>
-      <c r="B78" t="s">
-        <v>120</v>
-      </c>
-      <c r="C78" t="s">
-        <v>103</v>
-      </c>
-      <c r="D78" t="s">
-        <v>9</v>
-      </c>
-      <c r="F78" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A79" t="s">
+      <c r="B79" t="s">
+        <v>59</v>
+      </c>
+      <c r="C79" t="s">
+        <v>103</v>
+      </c>
+      <c r="F79" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>58</v>
+      </c>
+      <c r="B80" t="s">
+        <v>60</v>
+      </c>
+      <c r="C80" t="s">
+        <v>103</v>
+      </c>
+      <c r="E80" t="s">
+        <v>14</v>
+      </c>
+      <c r="F80" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
         <v>121</v>
       </c>
-      <c r="B79" t="s">
+      <c r="B81" t="s">
         <v>122</v>
       </c>
-      <c r="C79" t="s">
-        <v>103</v>
-      </c>
-      <c r="F79" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A80" t="s">
+      <c r="C81" t="s">
+        <v>103</v>
+      </c>
+      <c r="D81" t="s">
+        <v>9</v>
+      </c>
+      <c r="F81" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
         <v>123</v>
       </c>
-      <c r="B80" t="s">
+      <c r="B82" t="s">
         <v>124</v>
       </c>
-      <c r="C80" t="s">
-        <v>103</v>
-      </c>
-      <c r="F80" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A81" t="s">
+      <c r="C82" t="s">
+        <v>103</v>
+      </c>
+      <c r="F82" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A83" t="s">
         <v>125</v>
       </c>
-      <c r="B81" t="s">
+      <c r="B83" t="s">
         <v>126</v>
       </c>
-      <c r="C81" t="s">
-        <v>103</v>
-      </c>
-      <c r="F81" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A82" t="s">
+      <c r="C83" t="s">
+        <v>103</v>
+      </c>
+      <c r="F83" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A84" t="s">
         <v>127</v>
       </c>
-      <c r="B82" t="s">
+      <c r="B84" t="s">
         <v>128</v>
       </c>
-      <c r="C82" t="s">
-        <v>103</v>
-      </c>
-      <c r="F82" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A83" t="s">
+      <c r="C84" t="s">
+        <v>103</v>
+      </c>
+      <c r="F84" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A85" t="s">
         <v>129</v>
       </c>
-      <c r="B83" t="s">
+      <c r="B85" t="s">
         <v>130</v>
       </c>
-      <c r="C83" t="s">
-        <v>103</v>
-      </c>
-      <c r="D83" t="s">
-        <v>9</v>
-      </c>
-      <c r="F83" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A84" t="s">
-        <v>59</v>
-      </c>
-      <c r="B84" t="s">
-        <v>60</v>
-      </c>
-      <c r="C84" t="s">
-        <v>103</v>
-      </c>
-      <c r="D84" t="s">
-        <v>9</v>
-      </c>
-      <c r="E84" t="s">
-        <v>9</v>
-      </c>
-      <c r="F84" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A85" t="s">
+      <c r="C85" t="s">
+        <v>103</v>
+      </c>
+      <c r="F85" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A86" t="s">
+        <v>131</v>
+      </c>
+      <c r="B86" t="s">
+        <v>132</v>
+      </c>
+      <c r="C86" t="s">
+        <v>103</v>
+      </c>
+      <c r="D86" t="s">
+        <v>9</v>
+      </c>
+      <c r="F86" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A87" t="s">
         <v>61</v>
       </c>
-      <c r="B85" t="s">
+      <c r="B87" t="s">
         <v>62</v>
       </c>
-      <c r="C85" t="s">
-        <v>103</v>
-      </c>
-      <c r="F85" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A86" t="s">
-        <v>65</v>
-      </c>
-      <c r="B86" t="s">
-        <v>66</v>
-      </c>
-      <c r="C86" t="s">
-        <v>103</v>
-      </c>
-      <c r="D86" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A87" t="s">
+      <c r="C87" t="s">
+        <v>103</v>
+      </c>
+      <c r="D87" t="s">
+        <v>9</v>
+      </c>
+      <c r="E87" t="s">
+        <v>9</v>
+      </c>
+      <c r="F87" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A88" t="s">
+        <v>63</v>
+      </c>
+      <c r="B88" t="s">
+        <v>64</v>
+      </c>
+      <c r="C88" t="s">
+        <v>103</v>
+      </c>
+      <c r="F88" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A89" t="s">
         <v>67</v>
       </c>
-      <c r="B87" t="s">
+      <c r="B89" t="s">
         <v>68</v>
       </c>
-      <c r="C87" t="s">
-        <v>103</v>
-      </c>
-      <c r="D87" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A88" t="s">
+      <c r="C89" t="s">
+        <v>103</v>
+      </c>
+      <c r="D89" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A90" t="s">
         <v>69</v>
       </c>
-      <c r="B88" t="s">
+      <c r="B90" t="s">
         <v>70</v>
       </c>
-      <c r="C88" t="s">
-        <v>103</v>
-      </c>
-      <c r="D88" t="s">
-        <v>9</v>
-      </c>
-      <c r="F88" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A89" t="s">
+      <c r="C90" t="s">
+        <v>103</v>
+      </c>
+      <c r="D90" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A91" t="s">
         <v>71</v>
       </c>
-      <c r="B89" t="s">
+      <c r="B91" t="s">
         <v>72</v>
       </c>
-      <c r="C89" t="s">
-        <v>103</v>
-      </c>
-      <c r="D89" t="s">
-        <v>9</v>
-      </c>
-      <c r="F89" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A90" t="s">
+      <c r="C91" t="s">
+        <v>103</v>
+      </c>
+      <c r="D91" t="s">
+        <v>9</v>
+      </c>
+      <c r="F91" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A92" t="s">
         <v>73</v>
       </c>
-      <c r="B90" t="s">
+      <c r="B92" t="s">
         <v>74</v>
       </c>
-      <c r="C90" t="s">
-        <v>103</v>
-      </c>
-      <c r="D90" t="s">
-        <v>9</v>
-      </c>
-      <c r="E90" t="s">
-        <v>43</v>
-      </c>
-      <c r="F90" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A91" t="s">
-        <v>131</v>
-      </c>
-      <c r="B91" t="s">
-        <v>132</v>
-      </c>
-      <c r="C91" t="s">
-        <v>103</v>
-      </c>
-      <c r="D91" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A92" t="s">
+      <c r="C92" t="s">
+        <v>103</v>
+      </c>
+      <c r="D92" t="s">
+        <v>9</v>
+      </c>
+      <c r="F92" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A93" t="s">
+        <v>75</v>
+      </c>
+      <c r="B93" t="s">
+        <v>76</v>
+      </c>
+      <c r="C93" t="s">
+        <v>103</v>
+      </c>
+      <c r="D93" t="s">
+        <v>9</v>
+      </c>
+      <c r="E93" t="s">
+        <v>14</v>
+      </c>
+      <c r="F93" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A94" t="s">
         <v>133</v>
       </c>
-      <c r="B92" t="s">
+      <c r="B94" t="s">
         <v>134</v>
       </c>
-      <c r="C92" t="s">
-        <v>103</v>
-      </c>
-      <c r="D92" t="s">
-        <v>9</v>
-      </c>
-      <c r="E92" t="s">
-        <v>9</v>
-      </c>
-      <c r="F92" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A93" t="s">
+      <c r="C94" t="s">
+        <v>103</v>
+      </c>
+      <c r="D94" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A95" t="s">
         <v>135</v>
       </c>
-      <c r="B93" t="s">
+      <c r="B95" t="s">
         <v>136</v>
       </c>
-      <c r="C93" t="s">
-        <v>103</v>
-      </c>
-      <c r="D93" t="s">
-        <v>9</v>
-      </c>
-      <c r="F93" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A94" t="s">
+      <c r="C95" t="s">
+        <v>103</v>
+      </c>
+      <c r="D95" t="s">
+        <v>9</v>
+      </c>
+      <c r="E95" t="s">
+        <v>9</v>
+      </c>
+      <c r="F95" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A96" t="s">
         <v>137</v>
       </c>
-      <c r="B94" t="s">
+      <c r="B96" t="s">
         <v>138</v>
       </c>
-      <c r="C94" t="s">
-        <v>103</v>
-      </c>
-      <c r="D94" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A95" t="s">
+      <c r="C96" t="s">
+        <v>103</v>
+      </c>
+      <c r="D96" t="s">
+        <v>9</v>
+      </c>
+      <c r="F96" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A97" t="s">
         <v>139</v>
       </c>
-      <c r="B95" t="s">
+      <c r="B97" t="s">
         <v>140</v>
       </c>
-      <c r="C95" t="s">
-        <v>103</v>
-      </c>
-      <c r="D95" t="s">
-        <v>9</v>
-      </c>
-      <c r="E95" t="s">
-        <v>9</v>
-      </c>
-      <c r="F95" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A96" t="s">
+      <c r="C97" t="s">
+        <v>103</v>
+      </c>
+      <c r="D97" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A98" t="s">
         <v>141</v>
       </c>
-      <c r="B96" t="s">
+      <c r="B98" t="s">
         <v>142</v>
       </c>
-      <c r="C96" t="s">
-        <v>103</v>
-      </c>
-      <c r="D96" t="s">
-        <v>9</v>
-      </c>
-      <c r="F96" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A97" t="s">
-        <v>85</v>
-      </c>
-      <c r="B97" t="s">
-        <v>86</v>
-      </c>
-      <c r="C97" t="s">
-        <v>103</v>
-      </c>
-      <c r="D97" t="s">
-        <v>9</v>
-      </c>
-      <c r="F97" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A98" t="s">
-        <v>87</v>
-      </c>
-      <c r="B98" t="s">
-        <v>88</v>
-      </c>
       <c r="C98" t="s">
         <v>103</v>
       </c>
       <c r="D98" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E98" t="s">
+        <v>9</v>
+      </c>
+      <c r="F98" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>143</v>
       </c>
@@ -2406,77 +2407,125 @@
       <c r="D99" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F99" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
+        <v>87</v>
+      </c>
+      <c r="B100" t="s">
+        <v>88</v>
+      </c>
+      <c r="C100" t="s">
+        <v>103</v>
+      </c>
+      <c r="D100" t="s">
+        <v>9</v>
+      </c>
+      <c r="F100" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A101" t="s">
+        <v>89</v>
+      </c>
+      <c r="B101" t="s">
+        <v>90</v>
+      </c>
+      <c r="C101" t="s">
+        <v>103</v>
+      </c>
+      <c r="D101" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A102" t="s">
         <v>145</v>
       </c>
-      <c r="B100" t="s">
+      <c r="B102" t="s">
         <v>146</v>
       </c>
-      <c r="C100" t="s">
-        <v>103</v>
-      </c>
-      <c r="D100" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A101" t="s">
+      <c r="C102" t="s">
+        <v>103</v>
+      </c>
+      <c r="D102" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A103" t="s">
         <v>147</v>
       </c>
-      <c r="B101" t="s">
+      <c r="B103" t="s">
         <v>148</v>
       </c>
-      <c r="C101" t="s">
-        <v>103</v>
-      </c>
-      <c r="D101" t="s">
-        <v>9</v>
-      </c>
-      <c r="F101" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A102" t="s">
+      <c r="C103" t="s">
+        <v>103</v>
+      </c>
+      <c r="D103" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A104" t="s">
         <v>149</v>
       </c>
-      <c r="B102" t="s">
+      <c r="B104" t="s">
         <v>150</v>
       </c>
-      <c r="C102" t="s">
-        <v>103</v>
-      </c>
-      <c r="F102" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A103" t="s">
+      <c r="C104" t="s">
+        <v>103</v>
+      </c>
+      <c r="D104" t="s">
+        <v>9</v>
+      </c>
+      <c r="F104" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A105" t="s">
         <v>151</v>
       </c>
-      <c r="B103" t="s">
+      <c r="B105" t="s">
         <v>152</v>
       </c>
-      <c r="C103" t="s">
-        <v>103</v>
-      </c>
-      <c r="F103" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A104" t="s">
+      <c r="C105" t="s">
+        <v>103</v>
+      </c>
+      <c r="F105" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A106" t="s">
         <v>153</v>
       </c>
-      <c r="B104" t="s">
+      <c r="B106" t="s">
         <v>154</v>
       </c>
-      <c r="C104" t="s">
-        <v>103</v>
-      </c>
-      <c r="F104" t="s">
+      <c r="C106" t="s">
+        <v>103</v>
+      </c>
+      <c r="F106" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A107" t="s">
+        <v>155</v>
+      </c>
+      <c r="B107" t="s">
+        <v>156</v>
+      </c>
+      <c r="C107" t="s">
+        <v>103</v>
+      </c>
+      <c r="F107" t="s">
         <v>9</v>
       </c>
     </row>

--- a/html/Sygehus-EPJ-systemer_excel.XLSX
+++ b/html/Sygehus-EPJ-systemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38FB7C93-83BD-4FA1-B17B-177917427688}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3C4D9D3-902A-4602-96C1-E28E870442A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 20-02-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 04-03-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sygehus_EPJ_systemer">'Opdateret d. 20-02-2026'!$A$1:$F$107</definedName>
+    <definedName name="Sygehus_EPJ_systemer">'Opdateret d. 04-03-2026'!$A$1:$F$107</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Sygehus-EPJ-systemer_excel.XLSX
+++ b/html/Sygehus-EPJ-systemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3C4D9D3-902A-4602-96C1-E28E870442A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7658B8C7-604D-4CD5-AD28-B3377EE83614}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 04-03-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 06-03-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sygehus_EPJ_systemer">'Opdateret d. 04-03-2026'!$A$1:$F$107</definedName>
+    <definedName name="Sygehus_EPJ_systemer">'Opdateret d. 06-03-2026'!$A$1:$F$107</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Sygehus-EPJ-systemer_excel.XLSX
+++ b/html/Sygehus-EPJ-systemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7658B8C7-604D-4CD5-AD28-B3377EE83614}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C0C2710-A437-4F1E-9191-B279DEE96E09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Sygehus-EPJ-systemer_excel.XLSX
+++ b/html/Sygehus-EPJ-systemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C0C2710-A437-4F1E-9191-B279DEE96E09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D440D04-F03A-4C32-8269-8CBA58923267}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="Opdateret d. 06-03-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sygehus_EPJ_systemer">'Opdateret d. 06-03-2026'!$A$1:$F$107</definedName>
+    <definedName name="Sygehus_EPJ_systemer">'Opdateret d. 06-03-2026'!$A$1:$F$111</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="492" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="508" uniqueCount="159">
   <si>
     <t>Standard</t>
   </si>
@@ -263,6 +263,12 @@
     <t>XDIS05 (XD0533L)</t>
   </si>
   <si>
+    <t>BookingConfirmation</t>
+  </si>
+  <si>
+    <t>XDIS13 (XD1333L)</t>
+  </si>
+  <si>
     <t>MunicipalityLetter</t>
   </si>
   <si>
@@ -299,6 +305,12 @@
     <t>XREF01 (XH0131R)</t>
   </si>
   <si>
+    <t>XrayRequest</t>
+  </si>
+  <si>
+    <t>XREF02 (XH0231R)</t>
+  </si>
+  <si>
     <t>LaboratoryReport</t>
   </si>
   <si>
@@ -459,12 +471,6 @@
   </si>
   <si>
     <t>XDIS32 (XD3234L)</t>
-  </si>
-  <si>
-    <t>XrayRequest</t>
-  </si>
-  <si>
-    <t>XREF02 (XH0231R)</t>
   </si>
   <si>
     <t>PrivateSpecialistReferral</t>
@@ -836,7 +842,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F107"/>
+  <dimension ref="A1:F111"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
@@ -1450,9 +1456,6 @@
       <c r="D39" t="s">
         <v>9</v>
       </c>
-      <c r="F39" t="s">
-        <v>9</v>
-      </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
@@ -1467,9 +1470,6 @@
       <c r="D40" t="s">
         <v>9</v>
       </c>
-      <c r="E40" t="s">
-        <v>9</v>
-      </c>
       <c r="F40" t="s">
         <v>9</v>
       </c>
@@ -1484,6 +1484,12 @@
       <c r="C41" t="s">
         <v>8</v>
       </c>
+      <c r="D41" t="s">
+        <v>9</v>
+      </c>
+      <c r="E41" t="s">
+        <v>9</v>
+      </c>
       <c r="F41" t="s">
         <v>9</v>
       </c>
@@ -1498,7 +1504,7 @@
       <c r="C42" t="s">
         <v>8</v>
       </c>
-      <c r="E42" t="s">
+      <c r="F42" t="s">
         <v>9</v>
       </c>
     </row>
@@ -1512,11 +1518,8 @@
       <c r="C43" t="s">
         <v>8</v>
       </c>
-      <c r="D43" t="s">
-        <v>9</v>
-      </c>
-      <c r="F43" t="s">
-        <v>14</v>
+      <c r="E43" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
@@ -1532,6 +1535,9 @@
       <c r="D44" t="s">
         <v>9</v>
       </c>
+      <c r="F44" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
@@ -1543,30 +1549,30 @@
       <c r="C45" t="s">
         <v>8</v>
       </c>
-      <c r="F45" t="s">
+      <c r="D45" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B46" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C46" t="s">
         <v>8</v>
       </c>
-      <c r="F46" t="s">
+      <c r="D46" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B47" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C47" t="s">
         <v>8</v>
@@ -1577,10 +1583,10 @@
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B48" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C48" t="s">
         <v>8</v>
@@ -1591,10 +1597,10 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B49" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C49" t="s">
         <v>8</v>
@@ -1605,10 +1611,10 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B50" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C50" t="s">
         <v>8</v>
@@ -1619,10 +1625,10 @@
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B51" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C51" t="s">
         <v>8</v>
@@ -1633,10 +1639,10 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B52" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C52" t="s">
         <v>8</v>
@@ -1647,16 +1653,16 @@
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>6</v>
+        <v>104</v>
       </c>
       <c r="B53" t="s">
-        <v>7</v>
+        <v>105</v>
       </c>
       <c r="C53" t="s">
-        <v>103</v>
+        <v>8</v>
       </c>
       <c r="F53" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
@@ -1664,10 +1670,10 @@
         <v>104</v>
       </c>
       <c r="B54" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C54" t="s">
-        <v>103</v>
+        <v>8</v>
       </c>
       <c r="F54" t="s">
         <v>9</v>
@@ -1675,49 +1681,43 @@
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B55" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C55" t="s">
-        <v>103</v>
-      </c>
-      <c r="D55" t="s">
-        <v>9</v>
+        <v>107</v>
       </c>
       <c r="F55" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>12</v>
+        <v>108</v>
       </c>
       <c r="B56" t="s">
-        <v>13</v>
+        <v>109</v>
       </c>
       <c r="C56" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="F56" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="B57" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="C57" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="D57" t="s">
-        <v>9</v>
-      </c>
-      <c r="E57" t="s">
         <v>9</v>
       </c>
       <c r="F57" t="s">
@@ -1726,49 +1726,52 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="B58" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="C58" t="s">
-        <v>103</v>
-      </c>
-      <c r="D58" t="s">
-        <v>9</v>
-      </c>
-      <c r="E58" t="s">
-        <v>9</v>
+        <v>107</v>
       </c>
       <c r="F58" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>106</v>
+        <v>17</v>
       </c>
       <c r="B59" t="s">
-        <v>107</v>
+        <v>18</v>
       </c>
       <c r="C59" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="D59" t="s">
+        <v>9</v>
+      </c>
+      <c r="E59" t="s">
+        <v>9</v>
+      </c>
+      <c r="F59" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B60" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C60" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="D60" t="s">
+        <v>9</v>
+      </c>
+      <c r="E60" t="s">
         <v>9</v>
       </c>
       <c r="F60" t="s">
@@ -1777,27 +1780,27 @@
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>21</v>
+        <v>110</v>
       </c>
       <c r="B61" t="s">
-        <v>23</v>
+        <v>111</v>
       </c>
       <c r="C61" t="s">
-        <v>103</v>
-      </c>
-      <c r="E61" t="s">
-        <v>24</v>
+        <v>107</v>
+      </c>
+      <c r="D61" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B62" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C62" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="D62" t="s">
         <v>9</v>
@@ -1808,13 +1811,13 @@
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B63" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C63" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="E63" t="s">
         <v>24</v>
@@ -1822,13 +1825,13 @@
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B64" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C64" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="D64" t="s">
         <v>9</v>
@@ -1839,27 +1842,30 @@
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="B65" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C65" t="s">
-        <v>103</v>
-      </c>
-      <c r="F65" t="s">
-        <v>9</v>
+        <v>107</v>
+      </c>
+      <c r="E65" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="B66" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="C66" t="s">
-        <v>103</v>
+        <v>107</v>
+      </c>
+      <c r="D66" t="s">
+        <v>9</v>
       </c>
       <c r="F66" t="s">
         <v>9</v>
@@ -1867,13 +1873,13 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="B67" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="C67" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="F67" t="s">
         <v>9</v>
@@ -1881,16 +1887,13 @@
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>108</v>
+        <v>36</v>
       </c>
       <c r="B68" t="s">
-        <v>109</v>
+        <v>37</v>
       </c>
       <c r="C68" t="s">
-        <v>103</v>
-      </c>
-      <c r="D68" t="s">
-        <v>9</v>
+        <v>107</v>
       </c>
       <c r="F68" t="s">
         <v>9</v>
@@ -1898,19 +1901,13 @@
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>110</v>
+        <v>38</v>
       </c>
       <c r="B69" t="s">
-        <v>111</v>
+        <v>39</v>
       </c>
       <c r="C69" t="s">
-        <v>103</v>
-      </c>
-      <c r="D69" t="s">
-        <v>9</v>
-      </c>
-      <c r="E69" t="s">
-        <v>9</v>
+        <v>107</v>
       </c>
       <c r="F69" t="s">
         <v>9</v>
@@ -1918,18 +1915,15 @@
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>42</v>
+        <v>112</v>
       </c>
       <c r="B70" t="s">
-        <v>43</v>
+        <v>113</v>
       </c>
       <c r="C70" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="D70" t="s">
-        <v>9</v>
-      </c>
-      <c r="E70" t="s">
         <v>9</v>
       </c>
       <c r="F70" t="s">
@@ -1938,13 +1932,13 @@
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>44</v>
+        <v>114</v>
       </c>
       <c r="B71" t="s">
-        <v>45</v>
+        <v>115</v>
       </c>
       <c r="C71" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="D71" t="s">
         <v>9</v>
@@ -1958,15 +1952,18 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>112</v>
+        <v>42</v>
       </c>
       <c r="B72" t="s">
-        <v>113</v>
+        <v>43</v>
       </c>
       <c r="C72" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="D72" t="s">
+        <v>9</v>
+      </c>
+      <c r="E72" t="s">
         <v>9</v>
       </c>
       <c r="F72" t="s">
@@ -1975,13 +1972,19 @@
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>114</v>
+        <v>44</v>
       </c>
       <c r="B73" t="s">
-        <v>115</v>
+        <v>45</v>
       </c>
       <c r="C73" t="s">
-        <v>103</v>
+        <v>107</v>
+      </c>
+      <c r="D73" t="s">
+        <v>9</v>
+      </c>
+      <c r="E73" t="s">
+        <v>9</v>
       </c>
       <c r="F73" t="s">
         <v>9</v>
@@ -1995,7 +1998,7 @@
         <v>117</v>
       </c>
       <c r="C74" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="D74" t="s">
         <v>9</v>
@@ -2012,10 +2015,7 @@
         <v>119</v>
       </c>
       <c r="C75" t="s">
-        <v>103</v>
-      </c>
-      <c r="D75" t="s">
-        <v>9</v>
+        <v>107</v>
       </c>
       <c r="F75" t="s">
         <v>9</v>
@@ -2023,13 +2023,16 @@
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>53</v>
+        <v>120</v>
       </c>
       <c r="B76" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C76" t="s">
-        <v>103</v>
+        <v>107</v>
+      </c>
+      <c r="D76" t="s">
+        <v>9</v>
       </c>
       <c r="F76" t="s">
         <v>9</v>
@@ -2037,13 +2040,13 @@
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>55</v>
+        <v>122</v>
       </c>
       <c r="B77" t="s">
-        <v>56</v>
+        <v>123</v>
       </c>
       <c r="C77" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="D77" t="s">
         <v>9</v>
@@ -2054,19 +2057,13 @@
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B78" t="s">
-        <v>57</v>
+        <v>124</v>
       </c>
       <c r="C78" t="s">
-        <v>103</v>
-      </c>
-      <c r="D78" t="s">
-        <v>24</v>
-      </c>
-      <c r="E78" t="s">
-        <v>24</v>
+        <v>107</v>
       </c>
       <c r="F78" t="s">
         <v>9</v>
@@ -2074,13 +2071,16 @@
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="B79" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C79" t="s">
-        <v>103</v>
+        <v>107</v>
+      </c>
+      <c r="D79" t="s">
+        <v>9</v>
       </c>
       <c r="F79" t="s">
         <v>9</v>
@@ -2088,16 +2088,19 @@
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="B80" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C80" t="s">
-        <v>103</v>
+        <v>107</v>
+      </c>
+      <c r="D80" t="s">
+        <v>24</v>
       </c>
       <c r="E80" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="F80" t="s">
         <v>9</v>
@@ -2105,16 +2108,13 @@
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>121</v>
+        <v>58</v>
       </c>
       <c r="B81" t="s">
-        <v>122</v>
+        <v>59</v>
       </c>
       <c r="C81" t="s">
-        <v>103</v>
-      </c>
-      <c r="D81" t="s">
-        <v>9</v>
+        <v>107</v>
       </c>
       <c r="F81" t="s">
         <v>9</v>
@@ -2122,13 +2122,16 @@
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>123</v>
+        <v>58</v>
       </c>
       <c r="B82" t="s">
-        <v>124</v>
+        <v>60</v>
       </c>
       <c r="C82" t="s">
-        <v>103</v>
+        <v>107</v>
+      </c>
+      <c r="E82" t="s">
+        <v>14</v>
       </c>
       <c r="F82" t="s">
         <v>9</v>
@@ -2142,7 +2145,10 @@
         <v>126</v>
       </c>
       <c r="C83" t="s">
-        <v>103</v>
+        <v>107</v>
+      </c>
+      <c r="D83" t="s">
+        <v>9</v>
       </c>
       <c r="F83" t="s">
         <v>9</v>
@@ -2156,7 +2162,7 @@
         <v>128</v>
       </c>
       <c r="C84" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="F84" t="s">
         <v>9</v>
@@ -2170,7 +2176,7 @@
         <v>130</v>
       </c>
       <c r="C85" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="F85" t="s">
         <v>9</v>
@@ -2184,10 +2190,7 @@
         <v>132</v>
       </c>
       <c r="C86" t="s">
-        <v>103</v>
-      </c>
-      <c r="D86" t="s">
-        <v>9</v>
+        <v>107</v>
       </c>
       <c r="F86" t="s">
         <v>9</v>
@@ -2195,19 +2198,13 @@
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>61</v>
+        <v>133</v>
       </c>
       <c r="B87" t="s">
-        <v>62</v>
+        <v>134</v>
       </c>
       <c r="C87" t="s">
-        <v>103</v>
-      </c>
-      <c r="D87" t="s">
-        <v>9</v>
-      </c>
-      <c r="E87" t="s">
-        <v>9</v>
+        <v>107</v>
       </c>
       <c r="F87" t="s">
         <v>9</v>
@@ -2215,13 +2212,16 @@
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>63</v>
+        <v>135</v>
       </c>
       <c r="B88" t="s">
-        <v>64</v>
+        <v>136</v>
       </c>
       <c r="C88" t="s">
-        <v>103</v>
+        <v>107</v>
+      </c>
+      <c r="D88" t="s">
+        <v>9</v>
       </c>
       <c r="F88" t="s">
         <v>9</v>
@@ -2229,81 +2229,78 @@
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="B89" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="C89" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="D89" t="s">
+        <v>9</v>
+      </c>
+      <c r="E89" t="s">
+        <v>9</v>
+      </c>
+      <c r="F89" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="B90" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="C90" t="s">
-        <v>103</v>
-      </c>
-      <c r="D90" t="s">
+        <v>107</v>
+      </c>
+      <c r="F90" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B91" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C91" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="D91" t="s">
-        <v>9</v>
-      </c>
-      <c r="F91" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="B92" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C92" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="D92" t="s">
-        <v>9</v>
-      </c>
-      <c r="F92" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="B93" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C93" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="D93" t="s">
         <v>9</v>
-      </c>
-      <c r="E93" t="s">
-        <v>14</v>
       </c>
       <c r="F93" t="s">
         <v>9</v>
@@ -2311,33 +2308,36 @@
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>133</v>
+        <v>73</v>
       </c>
       <c r="B94" t="s">
-        <v>134</v>
+        <v>74</v>
       </c>
       <c r="C94" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="D94" t="s">
+        <v>9</v>
+      </c>
+      <c r="F94" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>135</v>
+        <v>75</v>
       </c>
       <c r="B95" t="s">
-        <v>136</v>
+        <v>76</v>
       </c>
       <c r="C95" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="D95" t="s">
         <v>9</v>
       </c>
       <c r="E95" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="F95" t="s">
         <v>9</v>
@@ -2345,30 +2345,27 @@
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>137</v>
+        <v>77</v>
       </c>
       <c r="B96" t="s">
-        <v>138</v>
+        <v>78</v>
       </c>
       <c r="C96" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="D96" t="s">
-        <v>9</v>
-      </c>
-      <c r="F96" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>139</v>
+        <v>79</v>
       </c>
       <c r="B97" t="s">
-        <v>140</v>
+        <v>80</v>
       </c>
       <c r="C97" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="D97" t="s">
         <v>9</v>
@@ -2376,35 +2373,32 @@
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="B98" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="C98" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="D98" t="s">
-        <v>9</v>
-      </c>
-      <c r="E98" t="s">
-        <v>9</v>
-      </c>
-      <c r="F98" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="B99" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="C99" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="D99" t="s">
+        <v>9</v>
+      </c>
+      <c r="E99" t="s">
         <v>9</v>
       </c>
       <c r="F99" t="s">
@@ -2413,13 +2407,13 @@
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>87</v>
+        <v>141</v>
       </c>
       <c r="B100" t="s">
-        <v>88</v>
+        <v>142</v>
       </c>
       <c r="C100" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="D100" t="s">
         <v>9</v>
@@ -2430,13 +2424,13 @@
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>89</v>
+        <v>143</v>
       </c>
       <c r="B101" t="s">
-        <v>90</v>
+        <v>144</v>
       </c>
       <c r="C101" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="D101" t="s">
         <v>9</v>
@@ -2450,9 +2444,15 @@
         <v>146</v>
       </c>
       <c r="C102" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="D102" t="s">
+        <v>9</v>
+      </c>
+      <c r="E102" t="s">
+        <v>9</v>
+      </c>
+      <c r="F102" t="s">
         <v>9</v>
       </c>
     </row>
@@ -2464,21 +2464,24 @@
         <v>148</v>
       </c>
       <c r="C103" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="D103" t="s">
+        <v>9</v>
+      </c>
+      <c r="F103" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>149</v>
+        <v>89</v>
       </c>
       <c r="B104" t="s">
-        <v>150</v>
+        <v>90</v>
       </c>
       <c r="C104" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="D104" t="s">
         <v>9</v>
@@ -2489,43 +2492,102 @@
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>151</v>
+        <v>91</v>
       </c>
       <c r="B105" t="s">
-        <v>152</v>
+        <v>92</v>
       </c>
       <c r="C105" t="s">
-        <v>103</v>
-      </c>
-      <c r="F105" t="s">
+        <v>107</v>
+      </c>
+      <c r="D105" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>153</v>
+        <v>93</v>
       </c>
       <c r="B106" t="s">
-        <v>154</v>
+        <v>94</v>
       </c>
       <c r="C106" t="s">
-        <v>103</v>
-      </c>
-      <c r="F106" t="s">
+        <v>107</v>
+      </c>
+      <c r="D106" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
+        <v>149</v>
+      </c>
+      <c r="B107" t="s">
+        <v>150</v>
+      </c>
+      <c r="C107" t="s">
+        <v>107</v>
+      </c>
+      <c r="D107" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A108" t="s">
+        <v>151</v>
+      </c>
+      <c r="B108" t="s">
+        <v>152</v>
+      </c>
+      <c r="C108" t="s">
+        <v>107</v>
+      </c>
+      <c r="D108" t="s">
+        <v>9</v>
+      </c>
+      <c r="F108" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A109" t="s">
+        <v>153</v>
+      </c>
+      <c r="B109" t="s">
+        <v>154</v>
+      </c>
+      <c r="C109" t="s">
+        <v>107</v>
+      </c>
+      <c r="F109" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A110" t="s">
         <v>155</v>
       </c>
-      <c r="B107" t="s">
+      <c r="B110" t="s">
         <v>156</v>
       </c>
-      <c r="C107" t="s">
-        <v>103</v>
-      </c>
-      <c r="F107" t="s">
+      <c r="C110" t="s">
+        <v>107</v>
+      </c>
+      <c r="F110" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A111" t="s">
+        <v>157</v>
+      </c>
+      <c r="B111" t="s">
+        <v>158</v>
+      </c>
+      <c r="C111" t="s">
+        <v>107</v>
+      </c>
+      <c r="F111" t="s">
         <v>9</v>
       </c>
     </row>

--- a/html/Sygehus-EPJ-systemer_excel.XLSX
+++ b/html/Sygehus-EPJ-systemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D440D04-F03A-4C32-8269-8CBA58923267}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B65EAD5F-035F-4B79-8635-0BA941338B24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14625" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 06-03-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 09-03-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sygehus_EPJ_systemer">'Opdateret d. 06-03-2026'!$A$1:$F$111</definedName>
+    <definedName name="Sygehus_EPJ_systemer">'Opdateret d. 09-03-2026'!$A$1:$F$111</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Sygehus-EPJ-systemer_excel.XLSX
+++ b/html/Sygehus-EPJ-systemer_excel.XLSX
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B65EAD5F-035F-4B79-8635-0BA941338B24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E83986DB-57A1-44EA-90DA-B80FB014BC18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14625" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 09-03-2026" sheetId="1" r:id="rId1"/>

--- a/html/Sygehus-EPJ-systemer_excel.XLSX
+++ b/html/Sygehus-EPJ-systemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E83986DB-57A1-44EA-90DA-B80FB014BC18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80EB0A6E-05B8-4D86-9073-BC58A9DDC8AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 09-03-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 11-03-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sygehus_EPJ_systemer">'Opdateret d. 09-03-2026'!$A$1:$F$111</definedName>
+    <definedName name="Sygehus_EPJ_systemer">'Opdateret d. 11-03-2026'!$A$1:$F$111</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Sygehus-EPJ-systemer_excel.XLSX
+++ b/html/Sygehus-EPJ-systemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80EB0A6E-05B8-4D86-9073-BC58A9DDC8AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8505CED-A4EA-4C75-8874-565067C32F7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Sygehus-EPJ-systemer_excel.XLSX
+++ b/html/Sygehus-EPJ-systemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8505CED-A4EA-4C75-8874-565067C32F7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41A4F786-0380-4901-AFCA-9237B838EDD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 11-03-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 20-03-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sygehus_EPJ_systemer">'Opdateret d. 11-03-2026'!$A$1:$F$111</definedName>
+    <definedName name="Sygehus_EPJ_systemer">'Opdateret d. 20-03-2026'!$A$1:$F$111</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Sygehus-EPJ-systemer_excel.XLSX
+++ b/html/Sygehus-EPJ-systemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41A4F786-0380-4901-AFCA-9237B838EDD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F078E2F8-67BF-4EFC-BDB8-B63B80733547}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 20-03-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 25-03-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sygehus_EPJ_systemer">'Opdateret d. 20-03-2026'!$A$1:$F$111</definedName>
+    <definedName name="Sygehus_EPJ_systemer">'Opdateret d. 25-03-2026'!$A$1:$F$111</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Sygehus-EPJ-systemer_excel.XLSX
+++ b/html/Sygehus-EPJ-systemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F078E2F8-67BF-4EFC-BDB8-B63B80733547}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{791D50A8-5443-4FAF-AE6B-352E9CAC29B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 25-03-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 08-04-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sygehus_EPJ_systemer">'Opdateret d. 25-03-2026'!$A$1:$F$111</definedName>
+    <definedName name="Sygehus_EPJ_systemer">'Opdateret d. 08-04-2026'!$A$1:$F$111</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Sygehus-EPJ-systemer_excel.XLSX
+++ b/html/Sygehus-EPJ-systemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{791D50A8-5443-4FAF-AE6B-352E9CAC29B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84775A54-C469-4E99-BE66-E88F331EF049}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 08-04-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 10-04-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sygehus_EPJ_systemer">'Opdateret d. 08-04-2026'!$A$1:$F$111</definedName>
+    <definedName name="Sygehus_EPJ_systemer">'Opdateret d. 10-04-2026'!$A$1:$F$111</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Sygehus-EPJ-systemer_excel.XLSX
+++ b/html/Sygehus-EPJ-systemer_excel.XLSX
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84775A54-C469-4E99-BE66-E88F331EF049}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D50CECC-C61E-40D9-9DF7-1E26FB26F3A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-15045" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 10-04-2026" sheetId="1" r:id="rId1"/>

--- a/html/Sygehus-EPJ-systemer_excel.XLSX
+++ b/html/Sygehus-EPJ-systemer_excel.XLSX
@@ -8,22 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D50CECC-C61E-40D9-9DF7-1E26FB26F3A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1427172F-4A21-42D3-B1B6-9DD72E9D494C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-15045" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 10-04-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 14-04-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sygehus_EPJ_systemer">'Opdateret d. 10-04-2026'!$A$1:$F$111</definedName>
+    <definedName name="Sygehus_EPJ_systemer">'Opdateret d. 14-04-2026'!$A$1:$F$111</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="508" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="511" uniqueCount="159">
   <si>
     <t>Standard</t>
   </si>
@@ -906,6 +906,9 @@
       <c r="C4" t="s">
         <v>8</v>
       </c>
+      <c r="D4" t="s">
+        <v>14</v>
+      </c>
       <c r="F4" t="s">
         <v>14</v>
       </c>
@@ -1689,6 +1692,9 @@
       <c r="C55" t="s">
         <v>107</v>
       </c>
+      <c r="D55" t="s">
+        <v>14</v>
+      </c>
       <c r="F55" t="s">
         <v>14</v>
       </c>
@@ -1733,6 +1739,9 @@
       </c>
       <c r="C58" t="s">
         <v>107</v>
+      </c>
+      <c r="D58" t="s">
+        <v>14</v>
       </c>
       <c r="F58" t="s">
         <v>14</v>

--- a/html/Sygehus-EPJ-systemer_excel.XLSX
+++ b/html/Sygehus-EPJ-systemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1427172F-4A21-42D3-B1B6-9DD72E9D494C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D86276FF-6144-4AFE-9065-94D0EC291425}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 14-04-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 24-04-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sygehus_EPJ_systemer">'Opdateret d. 14-04-2026'!$A$1:$F$111</definedName>
+    <definedName name="Sygehus_EPJ_systemer">'Opdateret d. 24-04-2026'!$A$1:$F$111</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Sygehus-EPJ-systemer_excel.XLSX
+++ b/html/Sygehus-EPJ-systemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D86276FF-6144-4AFE-9065-94D0EC291425}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFA559C6-F29A-45A0-952D-28311C29B96F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Sygehus-EPJ-systemer_excel.XLSX
+++ b/html/Sygehus-EPJ-systemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFA559C6-F29A-45A0-952D-28311C29B96F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4856A603-7EB8-4023-B049-A514AA11FAE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 24-04-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 27-04-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sygehus_EPJ_systemer">'Opdateret d. 24-04-2026'!$A$1:$F$111</definedName>
+    <definedName name="Sygehus_EPJ_systemer">'Opdateret d. 27-04-2026'!$A$1:$F$111</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -64,8 +64,7 @@
     <t>CareCommunication</t>
   </si>
   <si>
-    <t>CareCommunication (5.0_x000D_
-5.0)</t>
+    <t>CareCommunication (5.0)</t>
   </si>
   <si>
     <t>Tester</t>

--- a/html/Sygehus-EPJ-systemer_excel.XLSX
+++ b/html/Sygehus-EPJ-systemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4856A603-7EB8-4023-B049-A514AA11FAE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC54E744-588A-4352-84EE-B614D2C61337}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="384" yWindow="384" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 27-04-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 06-05-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sygehus_EPJ_systemer">'Opdateret d. 27-04-2026'!$A$1:$F$111</definedName>
+    <definedName name="Sygehus_EPJ_systemer">'Opdateret d. 06-05-2026'!$A$1:$F$111</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Sygehus-EPJ-systemer_excel.XLSX
+++ b/html/Sygehus-EPJ-systemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC54E744-588A-4352-84EE-B614D2C61337}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C982AB66-9B59-4331-ABC8-0730DC1DF8BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="384" yWindow="384" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 06-05-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 01-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sygehus_EPJ_systemer">'Opdateret d. 06-05-2026'!$A$1:$F$111</definedName>
+    <definedName name="Sygehus_EPJ_systemer">'Opdateret d. 01-06-2026'!$A$1:$F$111</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Sygehus-EPJ-systemer_excel.XLSX
+++ b/html/Sygehus-EPJ-systemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C982AB66-9B59-4331-ABC8-0730DC1DF8BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27B310DF-8196-4DFF-9054-D245C4CBE172}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 01-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 02-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sygehus_EPJ_systemer">'Opdateret d. 01-06-2026'!$A$1:$F$111</definedName>
+    <definedName name="Sygehus_EPJ_systemer">'Opdateret d. 02-06-2026'!$A$1:$F$111</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Sygehus-EPJ-systemer_excel.XLSX
+++ b/html/Sygehus-EPJ-systemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27B310DF-8196-4DFF-9054-D245C4CBE172}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9366BB87-AE18-4AC5-B5B0-355849E0F80B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Sygehus-EPJ-systemer_excel.XLSX
+++ b/html/Sygehus-EPJ-systemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9366BB87-AE18-4AC5-B5B0-355849E0F80B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D3163E3-3670-4BE3-93A7-B0C177315BBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 02-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 05-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sygehus_EPJ_systemer">'Opdateret d. 02-06-2026'!$A$1:$F$111</definedName>
+    <definedName name="Sygehus_EPJ_systemer">'Opdateret d. 05-06-2026'!$A$1:$F$111</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Sygehus-EPJ-systemer_excel.XLSX
+++ b/html/Sygehus-EPJ-systemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E411AEDA-C0BE-4C77-ABBB-1B75BF2A6ECC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43190489-71C7-4F57-B8C4-15FD5F3393D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Sygehus-EPJ-systemer_excel.XLSX
+++ b/html/Sygehus-EPJ-systemer_excel.XLSX
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E93F442F-7A0D-4641-A7D3-FDCB6EB1F677}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DE6F15D-BBAC-4F71-A24C-97F00E0616F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3150" yWindow="3135" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 09-06-2026" sheetId="1" r:id="rId1"/>

--- a/html/Sygehus-EPJ-systemer_excel.XLSX
+++ b/html/Sygehus-EPJ-systemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DE6F15D-BBAC-4F71-A24C-97F00E0616F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD9222AC-A721-45CD-B5A0-6BE88E820FD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Sygehus-EPJ-systemer_excel.XLSX
+++ b/html/Sygehus-EPJ-systemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD9222AC-A721-45CD-B5A0-6BE88E820FD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C0D5D40-4B8B-4C5A-B98C-CFFD39F4D7F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 09-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 15-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sygehus_EPJ_systemer">'Opdateret d. 09-06-2026'!$A$1:$F$111</definedName>
+    <definedName name="Sygehus_EPJ_systemer">'Opdateret d. 15-06-2026'!$A$1:$F$111</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -842,9 +842,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F111"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -864,7 +864,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -881,7 +881,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -895,7 +895,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -912,7 +912,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -932,7 +932,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>17</v>
       </c>
@@ -952,7 +952,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>19</v>
       </c>
@@ -972,7 +972,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>21</v>
       </c>
@@ -989,7 +989,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>21</v>
       </c>
@@ -1003,7 +1003,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>25</v>
       </c>
@@ -1020,7 +1020,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>25</v>
       </c>
@@ -1034,7 +1034,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>28</v>
       </c>
@@ -1051,7 +1051,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>30</v>
       </c>
@@ -1065,7 +1065,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>32</v>
       </c>
@@ -1079,7 +1079,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>34</v>
       </c>
@@ -1093,7 +1093,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>36</v>
       </c>
@@ -1107,7 +1107,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>38</v>
       </c>
@@ -1121,7 +1121,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>40</v>
       </c>
@@ -1135,7 +1135,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>42</v>
       </c>
@@ -1152,7 +1152,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>44</v>
       </c>
@@ -1172,7 +1172,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>46</v>
       </c>
@@ -1186,7 +1186,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>46</v>
       </c>
@@ -1203,7 +1203,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>49</v>
       </c>
@@ -1217,7 +1217,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>51</v>
       </c>
@@ -1231,7 +1231,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>53</v>
       </c>
@@ -1245,7 +1245,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>55</v>
       </c>
@@ -1262,7 +1262,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>55</v>
       </c>
@@ -1282,7 +1282,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>58</v>
       </c>
@@ -1296,7 +1296,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>58</v>
       </c>
@@ -1316,7 +1316,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>61</v>
       </c>
@@ -1333,7 +1333,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>63</v>
       </c>
@@ -1347,7 +1347,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>65</v>
       </c>
@@ -1361,7 +1361,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>67</v>
       </c>
@@ -1375,7 +1375,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>69</v>
       </c>
@@ -1389,7 +1389,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>71</v>
       </c>
@@ -1403,7 +1403,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>73</v>
       </c>
@@ -1417,7 +1417,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>75</v>
       </c>
@@ -1431,7 +1431,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>77</v>
       </c>
@@ -1445,7 +1445,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>79</v>
       </c>
@@ -1459,7 +1459,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>81</v>
       </c>
@@ -1476,7 +1476,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>83</v>
       </c>
@@ -1496,7 +1496,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>85</v>
       </c>
@@ -1510,7 +1510,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>87</v>
       </c>
@@ -1524,7 +1524,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>89</v>
       </c>
@@ -1541,7 +1541,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>91</v>
       </c>
@@ -1555,7 +1555,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>93</v>
       </c>
@@ -1569,7 +1569,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>95</v>
       </c>
@@ -1583,7 +1583,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>95</v>
       </c>
@@ -1597,7 +1597,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>98</v>
       </c>
@@ -1611,7 +1611,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>98</v>
       </c>
@@ -1625,7 +1625,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>101</v>
       </c>
@@ -1639,7 +1639,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>101</v>
       </c>
@@ -1653,7 +1653,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>104</v>
       </c>
@@ -1667,7 +1667,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>104</v>
       </c>
@@ -1681,7 +1681,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>6</v>
       </c>
@@ -1698,7 +1698,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>108</v>
       </c>
@@ -1712,7 +1712,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>10</v>
       </c>
@@ -1729,7 +1729,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>12</v>
       </c>
@@ -1746,7 +1746,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>17</v>
       </c>
@@ -1766,7 +1766,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>19</v>
       </c>
@@ -1786,7 +1786,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>110</v>
       </c>
@@ -1800,7 +1800,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>21</v>
       </c>
@@ -1817,7 +1817,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>21</v>
       </c>
@@ -1831,7 +1831,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>25</v>
       </c>
@@ -1848,7 +1848,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>25</v>
       </c>
@@ -1862,7 +1862,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>28</v>
       </c>
@@ -1879,7 +1879,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>30</v>
       </c>
@@ -1893,7 +1893,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>36</v>
       </c>
@@ -1907,7 +1907,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>38</v>
       </c>
@@ -1921,7 +1921,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>112</v>
       </c>
@@ -1938,7 +1938,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>114</v>
       </c>
@@ -1958,7 +1958,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>42</v>
       </c>
@@ -1978,7 +1978,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>44</v>
       </c>
@@ -1998,7 +1998,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>116</v>
       </c>
@@ -2015,7 +2015,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>118</v>
       </c>
@@ -2029,7 +2029,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>120</v>
       </c>
@@ -2046,7 +2046,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>122</v>
       </c>
@@ -2063,7 +2063,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>53</v>
       </c>
@@ -2077,7 +2077,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>55</v>
       </c>
@@ -2094,7 +2094,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>55</v>
       </c>
@@ -2114,7 +2114,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>58</v>
       </c>
@@ -2128,7 +2128,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>58</v>
       </c>
@@ -2145,7 +2145,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>125</v>
       </c>
@@ -2162,7 +2162,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>127</v>
       </c>
@@ -2176,7 +2176,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>129</v>
       </c>
@@ -2190,7 +2190,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>131</v>
       </c>
@@ -2204,7 +2204,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>133</v>
       </c>
@@ -2218,7 +2218,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>135</v>
       </c>
@@ -2235,7 +2235,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>61</v>
       </c>
@@ -2255,7 +2255,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>63</v>
       </c>
@@ -2269,7 +2269,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>67</v>
       </c>
@@ -2283,7 +2283,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>69</v>
       </c>
@@ -2297,7 +2297,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>71</v>
       </c>
@@ -2314,7 +2314,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>73</v>
       </c>
@@ -2331,7 +2331,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>75</v>
       </c>
@@ -2351,7 +2351,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>77</v>
       </c>
@@ -2365,7 +2365,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>79</v>
       </c>
@@ -2379,7 +2379,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>137</v>
       </c>
@@ -2393,7 +2393,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>139</v>
       </c>
@@ -2413,7 +2413,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>141</v>
       </c>
@@ -2430,7 +2430,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>143</v>
       </c>
@@ -2444,7 +2444,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>145</v>
       </c>
@@ -2464,7 +2464,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>147</v>
       </c>
@@ -2481,7 +2481,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>89</v>
       </c>
@@ -2498,7 +2498,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>91</v>
       </c>
@@ -2512,7 +2512,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>93</v>
       </c>
@@ -2526,7 +2526,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>149</v>
       </c>
@@ -2540,7 +2540,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>151</v>
       </c>
@@ -2557,7 +2557,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>153</v>
       </c>
@@ -2571,7 +2571,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>155</v>
       </c>
@@ -2585,7 +2585,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>157</v>
       </c>

--- a/html/Sygehus-EPJ-systemer_excel.XLSX
+++ b/html/Sygehus-EPJ-systemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C0D5D40-4B8B-4C5A-B98C-CFFD39F4D7F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{108A496A-D909-44CA-B65F-CC7EDE567C88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 15-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 22-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sygehus_EPJ_systemer">'Opdateret d. 15-06-2026'!$A$1:$F$111</definedName>
+    <definedName name="Sygehus_EPJ_systemer">'Opdateret d. 22-06-2026'!$A$1:$F$111</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Sygehus-EPJ-systemer_excel.XLSX
+++ b/html/Sygehus-EPJ-systemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{108A496A-D909-44CA-B65F-CC7EDE567C88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C5DABF3-42E1-4077-A165-A2C05254CE79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 22-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 23-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sygehus_EPJ_systemer">'Opdateret d. 22-06-2026'!$A$1:$F$111</definedName>
+    <definedName name="Sygehus_EPJ_systemer">'Opdateret d. 23-06-2026'!$A$1:$F$111</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -842,9 +842,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F111"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -864,7 +864,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -881,7 +881,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -895,7 +895,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -912,7 +912,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -932,7 +932,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>17</v>
       </c>
@@ -952,7 +952,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>19</v>
       </c>
@@ -972,7 +972,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>21</v>
       </c>
@@ -989,7 +989,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>21</v>
       </c>
@@ -1003,7 +1003,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>25</v>
       </c>
@@ -1020,7 +1020,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>25</v>
       </c>
@@ -1034,7 +1034,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>28</v>
       </c>
@@ -1051,7 +1051,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>30</v>
       </c>
@@ -1065,7 +1065,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>32</v>
       </c>
@@ -1079,7 +1079,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>34</v>
       </c>
@@ -1093,7 +1093,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>36</v>
       </c>
@@ -1107,7 +1107,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>38</v>
       </c>
@@ -1121,7 +1121,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>40</v>
       </c>
@@ -1135,7 +1135,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>42</v>
       </c>
@@ -1152,7 +1152,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>44</v>
       </c>
@@ -1172,7 +1172,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>46</v>
       </c>
@@ -1186,7 +1186,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>46</v>
       </c>
@@ -1203,7 +1203,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>49</v>
       </c>
@@ -1217,7 +1217,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>51</v>
       </c>
@@ -1231,7 +1231,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>53</v>
       </c>
@@ -1245,7 +1245,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>55</v>
       </c>
@@ -1262,7 +1262,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>55</v>
       </c>
@@ -1282,7 +1282,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>58</v>
       </c>
@@ -1296,7 +1296,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>58</v>
       </c>
@@ -1316,7 +1316,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>61</v>
       </c>
@@ -1333,7 +1333,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>63</v>
       </c>
@@ -1347,7 +1347,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>65</v>
       </c>
@@ -1361,7 +1361,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>67</v>
       </c>
@@ -1375,7 +1375,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>69</v>
       </c>
@@ -1389,7 +1389,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>71</v>
       </c>
@@ -1403,7 +1403,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>73</v>
       </c>
@@ -1417,7 +1417,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>75</v>
       </c>
@@ -1431,7 +1431,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>77</v>
       </c>
@@ -1445,7 +1445,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>79</v>
       </c>
@@ -1459,7 +1459,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>81</v>
       </c>
@@ -1476,7 +1476,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>83</v>
       </c>
@@ -1496,7 +1496,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>85</v>
       </c>
@@ -1510,7 +1510,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>87</v>
       </c>
@@ -1524,7 +1524,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>89</v>
       </c>
@@ -1541,7 +1541,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>91</v>
       </c>
@@ -1555,7 +1555,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>93</v>
       </c>
@@ -1569,7 +1569,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>95</v>
       </c>
@@ -1583,7 +1583,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>95</v>
       </c>
@@ -1597,7 +1597,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>98</v>
       </c>
@@ -1611,7 +1611,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>98</v>
       </c>
@@ -1625,7 +1625,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>101</v>
       </c>
@@ -1639,7 +1639,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>101</v>
       </c>
@@ -1653,7 +1653,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>104</v>
       </c>
@@ -1667,7 +1667,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>104</v>
       </c>
@@ -1681,7 +1681,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>6</v>
       </c>
@@ -1698,7 +1698,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>108</v>
       </c>
@@ -1712,7 +1712,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>10</v>
       </c>
@@ -1729,7 +1729,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>12</v>
       </c>
@@ -1746,7 +1746,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>17</v>
       </c>
@@ -1766,7 +1766,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>19</v>
       </c>
@@ -1786,7 +1786,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>110</v>
       </c>
@@ -1800,7 +1800,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>21</v>
       </c>
@@ -1817,7 +1817,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>21</v>
       </c>
@@ -1831,7 +1831,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>25</v>
       </c>
@@ -1848,7 +1848,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>25</v>
       </c>
@@ -1862,7 +1862,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>28</v>
       </c>
@@ -1879,7 +1879,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>30</v>
       </c>
@@ -1893,7 +1893,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>36</v>
       </c>
@@ -1907,7 +1907,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>38</v>
       </c>
@@ -1921,7 +1921,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>112</v>
       </c>
@@ -1938,7 +1938,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>114</v>
       </c>
@@ -1958,7 +1958,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>42</v>
       </c>
@@ -1978,7 +1978,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>44</v>
       </c>
@@ -1998,7 +1998,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>116</v>
       </c>
@@ -2015,7 +2015,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>118</v>
       </c>
@@ -2029,7 +2029,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>120</v>
       </c>
@@ -2046,7 +2046,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>122</v>
       </c>
@@ -2063,7 +2063,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>53</v>
       </c>
@@ -2077,7 +2077,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>55</v>
       </c>
@@ -2094,7 +2094,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>55</v>
       </c>
@@ -2114,7 +2114,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>58</v>
       </c>
@@ -2128,7 +2128,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>58</v>
       </c>
@@ -2145,7 +2145,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>125</v>
       </c>
@@ -2162,7 +2162,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>127</v>
       </c>
@@ -2176,7 +2176,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>129</v>
       </c>
@@ -2190,7 +2190,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>131</v>
       </c>
@@ -2204,7 +2204,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>133</v>
       </c>
@@ -2218,7 +2218,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>135</v>
       </c>
@@ -2235,7 +2235,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>61</v>
       </c>
@@ -2255,7 +2255,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>63</v>
       </c>
@@ -2269,7 +2269,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>67</v>
       </c>
@@ -2283,7 +2283,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>69</v>
       </c>
@@ -2297,7 +2297,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>71</v>
       </c>
@@ -2314,7 +2314,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>73</v>
       </c>
@@ -2331,7 +2331,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>75</v>
       </c>
@@ -2351,7 +2351,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>77</v>
       </c>
@@ -2365,7 +2365,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>79</v>
       </c>
@@ -2379,7 +2379,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>137</v>
       </c>
@@ -2393,7 +2393,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>139</v>
       </c>
@@ -2413,7 +2413,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>141</v>
       </c>
@@ -2430,7 +2430,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>143</v>
       </c>
@@ -2444,7 +2444,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>145</v>
       </c>
@@ -2464,7 +2464,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>147</v>
       </c>
@@ -2481,7 +2481,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>89</v>
       </c>
@@ -2498,7 +2498,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>91</v>
       </c>
@@ -2512,7 +2512,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>93</v>
       </c>
@@ -2526,7 +2526,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>149</v>
       </c>
@@ -2540,7 +2540,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>151</v>
       </c>
@@ -2557,7 +2557,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>153</v>
       </c>
@@ -2571,7 +2571,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>155</v>
       </c>
@@ -2585,7 +2585,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>157</v>
       </c>

--- a/html/Sygehus-EPJ-systemer_excel.XLSX
+++ b/html/Sygehus-EPJ-systemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C5DABF3-42E1-4077-A165-A2C05254CE79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3398EF2D-CA22-466C-A963-FC99D1678394}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Sygehus-EPJ-systemer_excel.XLSX
+++ b/html/Sygehus-EPJ-systemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{108A496A-D909-44CA-B65F-CC7EDE567C88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{108273EC-1465-4A4F-B4FC-AF817B4C3DC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2304" yWindow="2304" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 22-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 23-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sygehus_EPJ_systemer">'Opdateret d. 22-06-2026'!$A$1:$F$111</definedName>
+    <definedName name="Sygehus_EPJ_systemer">'Opdateret d. 23-06-2026'!$A$1:$F$111</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Sygehus-EPJ-systemer_excel.XLSX
+++ b/html/Sygehus-EPJ-systemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{108273EC-1465-4A4F-B4FC-AF817B4C3DC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3076204-899D-4766-B133-E1FCEED0F594}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2304" yWindow="2304" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 23-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 25-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sygehus_EPJ_systemer">'Opdateret d. 23-06-2026'!$A$1:$F$111</definedName>
+    <definedName name="Sygehus_EPJ_systemer">'Opdateret d. 25-06-2026'!$A$1:$F$111</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Sygehus-EPJ-systemer_excel.XLSX
+++ b/html/Sygehus-EPJ-systemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3076204-899D-4766-B133-E1FCEED0F594}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71AA1B17-87C3-4147-9DCE-940AA0CEB88F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2304" yWindow="2304" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 25-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 30-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sygehus_EPJ_systemer">'Opdateret d. 25-06-2026'!$A$1:$F$111</definedName>
+    <definedName name="Sygehus_EPJ_systemer">'Opdateret d. 30-06-2026'!$A$1:$F$111</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Sygehus-EPJ-systemer_excel.XLSX
+++ b/html/Sygehus-EPJ-systemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71AA1B17-87C3-4147-9DCE-940AA0CEB88F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1A1F8CF-F9C0-45D6-9253-FE079F23AAFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Sygehus-EPJ-systemer_excel.XLSX
+++ b/html/Sygehus-EPJ-systemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1A1F8CF-F9C0-45D6-9253-FE079F23AAFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D84FC426-3B96-44F4-BA76-6A7D26347E1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 30-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 01-07-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sygehus_EPJ_systemer">'Opdateret d. 30-06-2026'!$A$1:$F$111</definedName>
+    <definedName name="Sygehus_EPJ_systemer">'Opdateret d. 01-07-2026'!$A$1:$F$111</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -842,9 +842,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F111"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -864,7 +864,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -881,7 +881,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -895,7 +895,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -912,7 +912,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -932,7 +932,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>17</v>
       </c>
@@ -952,7 +952,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>19</v>
       </c>
@@ -972,7 +972,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>21</v>
       </c>
@@ -989,7 +989,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>21</v>
       </c>
@@ -1003,7 +1003,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>25</v>
       </c>
@@ -1020,7 +1020,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>25</v>
       </c>
@@ -1034,7 +1034,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>28</v>
       </c>
@@ -1051,7 +1051,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>30</v>
       </c>
@@ -1065,7 +1065,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>32</v>
       </c>
@@ -1079,7 +1079,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>34</v>
       </c>
@@ -1093,7 +1093,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>36</v>
       </c>
@@ -1107,7 +1107,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>38</v>
       </c>
@@ -1121,7 +1121,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>40</v>
       </c>
@@ -1135,7 +1135,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>42</v>
       </c>
@@ -1152,7 +1152,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>44</v>
       </c>
@@ -1172,7 +1172,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>46</v>
       </c>
@@ -1186,7 +1186,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>46</v>
       </c>
@@ -1203,7 +1203,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>49</v>
       </c>
@@ -1217,7 +1217,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>51</v>
       </c>
@@ -1231,7 +1231,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>53</v>
       </c>
@@ -1245,7 +1245,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>55</v>
       </c>
@@ -1262,7 +1262,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>55</v>
       </c>
@@ -1282,7 +1282,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>58</v>
       </c>
@@ -1296,7 +1296,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>58</v>
       </c>
@@ -1316,7 +1316,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>61</v>
       </c>
@@ -1333,7 +1333,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>63</v>
       </c>
@@ -1347,7 +1347,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>65</v>
       </c>
@@ -1361,7 +1361,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>67</v>
       </c>
@@ -1375,7 +1375,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>69</v>
       </c>
@@ -1389,7 +1389,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>71</v>
       </c>
@@ -1403,7 +1403,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>73</v>
       </c>
@@ -1417,7 +1417,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>75</v>
       </c>
@@ -1431,7 +1431,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>77</v>
       </c>
@@ -1445,7 +1445,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>79</v>
       </c>
@@ -1459,7 +1459,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>81</v>
       </c>
@@ -1476,7 +1476,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>83</v>
       </c>
@@ -1496,7 +1496,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>85</v>
       </c>
@@ -1510,7 +1510,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>87</v>
       </c>
@@ -1524,7 +1524,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>89</v>
       </c>
@@ -1541,7 +1541,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>91</v>
       </c>
@@ -1555,7 +1555,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>93</v>
       </c>
@@ -1569,7 +1569,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>95</v>
       </c>
@@ -1583,7 +1583,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>95</v>
       </c>
@@ -1597,7 +1597,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>98</v>
       </c>
@@ -1611,7 +1611,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>98</v>
       </c>
@@ -1625,7 +1625,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>101</v>
       </c>
@@ -1639,7 +1639,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>101</v>
       </c>
@@ -1653,7 +1653,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>104</v>
       </c>
@@ -1667,7 +1667,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>104</v>
       </c>
@@ -1681,7 +1681,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>6</v>
       </c>
@@ -1698,7 +1698,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>108</v>
       </c>
@@ -1712,7 +1712,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>10</v>
       </c>
@@ -1729,7 +1729,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>12</v>
       </c>
@@ -1746,7 +1746,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>17</v>
       </c>
@@ -1766,7 +1766,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>19</v>
       </c>
@@ -1786,7 +1786,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>110</v>
       </c>
@@ -1800,7 +1800,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>21</v>
       </c>
@@ -1817,7 +1817,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>21</v>
       </c>
@@ -1831,7 +1831,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>25</v>
       </c>
@@ -1848,7 +1848,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>25</v>
       </c>
@@ -1862,7 +1862,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>28</v>
       </c>
@@ -1879,7 +1879,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>30</v>
       </c>
@@ -1893,7 +1893,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>36</v>
       </c>
@@ -1907,7 +1907,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>38</v>
       </c>
@@ -1921,7 +1921,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>112</v>
       </c>
@@ -1938,7 +1938,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>114</v>
       </c>
@@ -1958,7 +1958,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>42</v>
       </c>
@@ -1978,7 +1978,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>44</v>
       </c>
@@ -1998,7 +1998,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>116</v>
       </c>
@@ -2015,7 +2015,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>118</v>
       </c>
@@ -2029,7 +2029,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>120</v>
       </c>
@@ -2046,7 +2046,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>122</v>
       </c>
@@ -2063,7 +2063,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>53</v>
       </c>
@@ -2077,7 +2077,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>55</v>
       </c>
@@ -2094,7 +2094,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>55</v>
       </c>
@@ -2114,7 +2114,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>58</v>
       </c>
@@ -2128,7 +2128,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>58</v>
       </c>
@@ -2145,7 +2145,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>125</v>
       </c>
@@ -2162,7 +2162,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>127</v>
       </c>
@@ -2176,7 +2176,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>129</v>
       </c>
@@ -2190,7 +2190,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>131</v>
       </c>
@@ -2204,7 +2204,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>133</v>
       </c>
@@ -2218,7 +2218,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>135</v>
       </c>
@@ -2235,7 +2235,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>61</v>
       </c>
@@ -2255,7 +2255,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>63</v>
       </c>
@@ -2269,7 +2269,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>67</v>
       </c>
@@ -2283,7 +2283,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>69</v>
       </c>
@@ -2297,7 +2297,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>71</v>
       </c>
@@ -2314,7 +2314,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>73</v>
       </c>
@@ -2331,7 +2331,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>75</v>
       </c>
@@ -2351,7 +2351,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>77</v>
       </c>
@@ -2365,7 +2365,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>79</v>
       </c>
@@ -2379,7 +2379,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>137</v>
       </c>
@@ -2393,7 +2393,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>139</v>
       </c>
@@ -2413,7 +2413,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>141</v>
       </c>
@@ -2430,7 +2430,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>143</v>
       </c>
@@ -2444,7 +2444,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>145</v>
       </c>
@@ -2464,7 +2464,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>147</v>
       </c>
@@ -2481,7 +2481,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>89</v>
       </c>
@@ -2498,7 +2498,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>91</v>
       </c>
@@ -2512,7 +2512,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>93</v>
       </c>
@@ -2526,7 +2526,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>149</v>
       </c>
@@ -2540,7 +2540,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>151</v>
       </c>
@@ -2557,7 +2557,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>153</v>
       </c>
@@ -2571,7 +2571,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>155</v>
       </c>
@@ -2585,7 +2585,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>157</v>
       </c>

--- a/html/Sygehus-EPJ-systemer_excel.XLSX
+++ b/html/Sygehus-EPJ-systemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D84FC426-3B96-44F4-BA76-6A7D26347E1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{177C6019-024A-4A8C-8969-981D5E287EEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 01-07-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 02-07-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sygehus_EPJ_systemer">'Opdateret d. 01-07-2026'!$A$1:$F$111</definedName>
+    <definedName name="Sygehus_EPJ_systemer">'Opdateret d. 02-07-2026'!$A$1:$F$111</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Sygehus-EPJ-systemer_excel.XLSX
+++ b/html/Sygehus-EPJ-systemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D84FC426-3B96-44F4-BA76-6A7D26347E1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{925320EB-2FF7-4A79-8B8B-D4E919D25ABA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 01-07-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 03-07-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sygehus_EPJ_systemer">'Opdateret d. 01-07-2026'!$A$1:$F$111</definedName>
+    <definedName name="Sygehus_EPJ_systemer">'Opdateret d. 03-07-2026'!$A$1:$F$111</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -842,9 +842,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F111"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -864,7 +864,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -881,7 +881,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -895,7 +895,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -906,13 +906,13 @@
         <v>8</v>
       </c>
       <c r="D4" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="F4" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -932,7 +932,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>17</v>
       </c>
@@ -952,7 +952,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>19</v>
       </c>
@@ -972,7 +972,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>21</v>
       </c>
@@ -989,7 +989,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>21</v>
       </c>
@@ -1003,7 +1003,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>25</v>
       </c>
@@ -1020,7 +1020,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>25</v>
       </c>
@@ -1034,7 +1034,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>28</v>
       </c>
@@ -1051,7 +1051,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>30</v>
       </c>
@@ -1065,7 +1065,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>32</v>
       </c>
@@ -1079,7 +1079,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>34</v>
       </c>
@@ -1093,7 +1093,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>36</v>
       </c>
@@ -1107,7 +1107,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>38</v>
       </c>
@@ -1121,7 +1121,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>40</v>
       </c>
@@ -1135,7 +1135,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>42</v>
       </c>
@@ -1152,7 +1152,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>44</v>
       </c>
@@ -1172,7 +1172,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>46</v>
       </c>
@@ -1186,7 +1186,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>46</v>
       </c>
@@ -1203,7 +1203,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>49</v>
       </c>
@@ -1217,7 +1217,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>51</v>
       </c>
@@ -1231,7 +1231,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>53</v>
       </c>
@@ -1245,7 +1245,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>55</v>
       </c>
@@ -1262,7 +1262,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>55</v>
       </c>
@@ -1282,7 +1282,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>58</v>
       </c>
@@ -1296,7 +1296,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>58</v>
       </c>
@@ -1316,7 +1316,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>61</v>
       </c>
@@ -1333,7 +1333,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>63</v>
       </c>
@@ -1347,7 +1347,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>65</v>
       </c>
@@ -1361,7 +1361,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>67</v>
       </c>
@@ -1375,7 +1375,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>69</v>
       </c>
@@ -1389,7 +1389,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>71</v>
       </c>
@@ -1403,7 +1403,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>73</v>
       </c>
@@ -1417,7 +1417,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>75</v>
       </c>
@@ -1431,7 +1431,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>77</v>
       </c>
@@ -1445,7 +1445,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>79</v>
       </c>
@@ -1459,7 +1459,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>81</v>
       </c>
@@ -1476,7 +1476,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>83</v>
       </c>
@@ -1496,7 +1496,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>85</v>
       </c>
@@ -1510,7 +1510,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>87</v>
       </c>
@@ -1524,7 +1524,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>89</v>
       </c>
@@ -1541,7 +1541,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>91</v>
       </c>
@@ -1555,7 +1555,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>93</v>
       </c>
@@ -1569,7 +1569,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>95</v>
       </c>
@@ -1583,7 +1583,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>95</v>
       </c>
@@ -1597,7 +1597,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>98</v>
       </c>
@@ -1611,7 +1611,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>98</v>
       </c>
@@ -1625,7 +1625,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>101</v>
       </c>
@@ -1639,7 +1639,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>101</v>
       </c>
@@ -1653,7 +1653,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>104</v>
       </c>
@@ -1667,7 +1667,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>104</v>
       </c>
@@ -1681,7 +1681,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>6</v>
       </c>
@@ -1692,13 +1692,13 @@
         <v>107</v>
       </c>
       <c r="D55" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="F55" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>108</v>
       </c>
@@ -1712,7 +1712,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>10</v>
       </c>
@@ -1729,7 +1729,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>12</v>
       </c>
@@ -1740,13 +1740,13 @@
         <v>107</v>
       </c>
       <c r="D58" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="F58" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>17</v>
       </c>
@@ -1766,7 +1766,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>19</v>
       </c>
@@ -1786,7 +1786,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>110</v>
       </c>
@@ -1800,7 +1800,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>21</v>
       </c>
@@ -1817,7 +1817,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>21</v>
       </c>
@@ -1831,7 +1831,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>25</v>
       </c>
@@ -1848,7 +1848,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>25</v>
       </c>
@@ -1862,7 +1862,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>28</v>
       </c>
@@ -1879,7 +1879,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>30</v>
       </c>
@@ -1893,7 +1893,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>36</v>
       </c>
@@ -1907,7 +1907,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>38</v>
       </c>
@@ -1921,7 +1921,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>112</v>
       </c>
@@ -1938,7 +1938,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>114</v>
       </c>
@@ -1958,7 +1958,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>42</v>
       </c>
@@ -1978,7 +1978,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>44</v>
       </c>
@@ -1998,7 +1998,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>116</v>
       </c>
@@ -2015,7 +2015,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>118</v>
       </c>
@@ -2029,7 +2029,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>120</v>
       </c>
@@ -2046,7 +2046,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>122</v>
       </c>
@@ -2063,7 +2063,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>53</v>
       </c>
@@ -2077,7 +2077,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>55</v>
       </c>
@@ -2094,7 +2094,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>55</v>
       </c>
@@ -2114,7 +2114,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>58</v>
       </c>
@@ -2128,7 +2128,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>58</v>
       </c>
@@ -2145,7 +2145,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>125</v>
       </c>
@@ -2162,7 +2162,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>127</v>
       </c>
@@ -2176,7 +2176,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>129</v>
       </c>
@@ -2190,7 +2190,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>131</v>
       </c>
@@ -2204,7 +2204,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>133</v>
       </c>
@@ -2218,7 +2218,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>135</v>
       </c>
@@ -2235,7 +2235,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>61</v>
       </c>
@@ -2255,7 +2255,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>63</v>
       </c>
@@ -2269,7 +2269,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>67</v>
       </c>
@@ -2283,7 +2283,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>69</v>
       </c>
@@ -2297,7 +2297,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>71</v>
       </c>
@@ -2314,7 +2314,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>73</v>
       </c>
@@ -2331,7 +2331,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>75</v>
       </c>
@@ -2351,7 +2351,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>77</v>
       </c>
@@ -2365,7 +2365,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>79</v>
       </c>
@@ -2379,7 +2379,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>137</v>
       </c>
@@ -2393,7 +2393,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>139</v>
       </c>
@@ -2413,7 +2413,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>141</v>
       </c>
@@ -2430,7 +2430,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>143</v>
       </c>
@@ -2444,7 +2444,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>145</v>
       </c>
@@ -2464,7 +2464,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>147</v>
       </c>
@@ -2481,7 +2481,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>89</v>
       </c>
@@ -2498,7 +2498,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>91</v>
       </c>
@@ -2512,7 +2512,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>93</v>
       </c>
@@ -2526,7 +2526,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>149</v>
       </c>
@@ -2540,7 +2540,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>151</v>
       </c>
@@ -2557,7 +2557,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>153</v>
       </c>
@@ -2571,7 +2571,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>155</v>
       </c>
@@ -2585,7 +2585,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>157</v>
       </c>

--- a/html/Sygehus-EPJ-systemer_excel.XLSX
+++ b/html/Sygehus-EPJ-systemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{177C6019-024A-4A8C-8969-981D5E287EEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFD10E83-55B5-45A5-999C-36C22927D569}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 02-07-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 03-07-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sygehus_EPJ_systemer">'Opdateret d. 02-07-2026'!$A$1:$F$111</definedName>
+    <definedName name="Sygehus_EPJ_systemer">'Opdateret d. 03-07-2026'!$A$1:$F$111</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -842,9 +842,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F111"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -864,7 +864,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -881,7 +881,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -895,7 +895,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -906,13 +906,13 @@
         <v>8</v>
       </c>
       <c r="D4" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="F4" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -932,7 +932,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>17</v>
       </c>
@@ -952,7 +952,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>19</v>
       </c>
@@ -972,7 +972,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>21</v>
       </c>
@@ -989,7 +989,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>21</v>
       </c>
@@ -1003,7 +1003,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>25</v>
       </c>
@@ -1020,7 +1020,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>25</v>
       </c>
@@ -1034,7 +1034,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>28</v>
       </c>
@@ -1051,7 +1051,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>30</v>
       </c>
@@ -1065,7 +1065,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>32</v>
       </c>
@@ -1079,7 +1079,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>34</v>
       </c>
@@ -1093,7 +1093,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>36</v>
       </c>
@@ -1107,7 +1107,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>38</v>
       </c>
@@ -1121,7 +1121,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>40</v>
       </c>
@@ -1135,7 +1135,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>42</v>
       </c>
@@ -1152,7 +1152,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>44</v>
       </c>
@@ -1172,7 +1172,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>46</v>
       </c>
@@ -1186,7 +1186,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>46</v>
       </c>
@@ -1203,7 +1203,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>49</v>
       </c>
@@ -1217,7 +1217,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>51</v>
       </c>
@@ -1231,7 +1231,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>53</v>
       </c>
@@ -1245,7 +1245,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>55</v>
       </c>
@@ -1262,7 +1262,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>55</v>
       </c>
@@ -1282,7 +1282,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>58</v>
       </c>
@@ -1296,7 +1296,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>58</v>
       </c>
@@ -1316,7 +1316,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>61</v>
       </c>
@@ -1333,7 +1333,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>63</v>
       </c>
@@ -1347,7 +1347,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>65</v>
       </c>
@@ -1361,7 +1361,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>67</v>
       </c>
@@ -1375,7 +1375,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>69</v>
       </c>
@@ -1389,7 +1389,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>71</v>
       </c>
@@ -1403,7 +1403,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>73</v>
       </c>
@@ -1417,7 +1417,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>75</v>
       </c>
@@ -1431,7 +1431,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>77</v>
       </c>
@@ -1445,7 +1445,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>79</v>
       </c>
@@ -1459,7 +1459,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>81</v>
       </c>
@@ -1476,7 +1476,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>83</v>
       </c>
@@ -1496,7 +1496,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>85</v>
       </c>
@@ -1510,7 +1510,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>87</v>
       </c>
@@ -1524,7 +1524,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>89</v>
       </c>
@@ -1541,7 +1541,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>91</v>
       </c>
@@ -1555,7 +1555,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>93</v>
       </c>
@@ -1569,7 +1569,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>95</v>
       </c>
@@ -1583,7 +1583,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>95</v>
       </c>
@@ -1597,7 +1597,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>98</v>
       </c>
@@ -1611,7 +1611,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>98</v>
       </c>
@@ -1625,7 +1625,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>101</v>
       </c>
@@ -1639,7 +1639,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>101</v>
       </c>
@@ -1653,7 +1653,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>104</v>
       </c>
@@ -1667,7 +1667,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>104</v>
       </c>
@@ -1681,7 +1681,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>6</v>
       </c>
@@ -1692,13 +1692,13 @@
         <v>107</v>
       </c>
       <c r="D55" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="F55" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>108</v>
       </c>
@@ -1712,7 +1712,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>10</v>
       </c>
@@ -1729,7 +1729,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>12</v>
       </c>
@@ -1740,13 +1740,13 @@
         <v>107</v>
       </c>
       <c r="D58" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="F58" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>17</v>
       </c>
@@ -1766,7 +1766,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>19</v>
       </c>
@@ -1786,7 +1786,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>110</v>
       </c>
@@ -1800,7 +1800,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>21</v>
       </c>
@@ -1817,7 +1817,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>21</v>
       </c>
@@ -1831,7 +1831,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>25</v>
       </c>
@@ -1848,7 +1848,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>25</v>
       </c>
@@ -1862,7 +1862,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>28</v>
       </c>
@@ -1879,7 +1879,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>30</v>
       </c>
@@ -1893,7 +1893,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>36</v>
       </c>
@@ -1907,7 +1907,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>38</v>
       </c>
@@ -1921,7 +1921,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>112</v>
       </c>
@@ -1938,7 +1938,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>114</v>
       </c>
@@ -1958,7 +1958,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>42</v>
       </c>
@@ -1978,7 +1978,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>44</v>
       </c>
@@ -1998,7 +1998,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>116</v>
       </c>
@@ -2015,7 +2015,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>118</v>
       </c>
@@ -2029,7 +2029,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>120</v>
       </c>
@@ -2046,7 +2046,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>122</v>
       </c>
@@ -2063,7 +2063,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>53</v>
       </c>
@@ -2077,7 +2077,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>55</v>
       </c>
@@ -2094,7 +2094,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>55</v>
       </c>
@@ -2114,7 +2114,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>58</v>
       </c>
@@ -2128,7 +2128,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>58</v>
       </c>
@@ -2145,7 +2145,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>125</v>
       </c>
@@ -2162,7 +2162,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>127</v>
       </c>
@@ -2176,7 +2176,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>129</v>
       </c>
@@ -2190,7 +2190,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>131</v>
       </c>
@@ -2204,7 +2204,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>133</v>
       </c>
@@ -2218,7 +2218,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>135</v>
       </c>
@@ -2235,7 +2235,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>61</v>
       </c>
@@ -2255,7 +2255,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>63</v>
       </c>
@@ -2269,7 +2269,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>67</v>
       </c>
@@ -2283,7 +2283,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>69</v>
       </c>
@@ -2297,7 +2297,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>71</v>
       </c>
@@ -2314,7 +2314,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>73</v>
       </c>
@@ -2331,7 +2331,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>75</v>
       </c>
@@ -2351,7 +2351,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>77</v>
       </c>
@@ -2365,7 +2365,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>79</v>
       </c>
@@ -2379,7 +2379,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>137</v>
       </c>
@@ -2393,7 +2393,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>139</v>
       </c>
@@ -2413,7 +2413,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>141</v>
       </c>
@@ -2430,7 +2430,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>143</v>
       </c>
@@ -2444,7 +2444,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>145</v>
       </c>
@@ -2464,7 +2464,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>147</v>
       </c>
@@ -2481,7 +2481,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>89</v>
       </c>
@@ -2498,7 +2498,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>91</v>
       </c>
@@ -2512,7 +2512,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>93</v>
       </c>
@@ -2526,7 +2526,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>149</v>
       </c>
@@ -2540,7 +2540,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>151</v>
       </c>
@@ -2557,7 +2557,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>153</v>
       </c>
@@ -2571,7 +2571,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>155</v>
       </c>
@@ -2585,7 +2585,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>157</v>
       </c>

--- a/html/Sygehus-EPJ-systemer_excel.XLSX
+++ b/html/Sygehus-EPJ-systemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFD10E83-55B5-45A5-999C-36C22927D569}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1AC4481-2AD7-4344-8E31-78D6F30B529C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 03-07-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 09-07-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sygehus_EPJ_systemer">'Opdateret d. 03-07-2026'!$A$1:$F$111</definedName>
+    <definedName name="Sygehus_EPJ_systemer">'Opdateret d. 09-07-2026'!$A$1:$F$111</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Sygehus-EPJ-systemer_excel.XLSX
+++ b/html/Sygehus-EPJ-systemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1AC4481-2AD7-4344-8E31-78D6F30B529C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5973ABD-36B8-4A8B-B1C7-129F3F4D3C4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 09-07-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 19-08-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sygehus_EPJ_systemer">'Opdateret d. 09-07-2026'!$A$1:$F$111</definedName>
+    <definedName name="Sygehus_EPJ_systemer">'Opdateret d. 19-08-2026'!$A$1:$F$111</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Sygehus-EPJ-systemer_excel.XLSX
+++ b/html/Sygehus-EPJ-systemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5973ABD-36B8-4A8B-B1C7-129F3F4D3C4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A016F9C-07C1-4B3D-BCA7-55912B3031F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4560" yWindow="945" windowWidth="21600" windowHeight="12450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 19-08-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 21-08-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sygehus_EPJ_systemer">'Opdateret d. 19-08-2026'!$A$1:$F$111</definedName>
+    <definedName name="Sygehus_EPJ_systemer">'Opdateret d. 21-08-2026'!$A$1:$F$111</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -842,9 +842,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F111"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -864,7 +864,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -881,7 +881,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -895,7 +895,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -912,7 +912,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -932,7 +932,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>17</v>
       </c>
@@ -952,7 +952,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>19</v>
       </c>
@@ -972,7 +972,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>21</v>
       </c>
@@ -989,7 +989,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>21</v>
       </c>
@@ -1003,7 +1003,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>25</v>
       </c>
@@ -1020,7 +1020,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>25</v>
       </c>
@@ -1034,7 +1034,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>28</v>
       </c>
@@ -1051,7 +1051,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>30</v>
       </c>
@@ -1065,7 +1065,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>32</v>
       </c>
@@ -1079,7 +1079,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>34</v>
       </c>
@@ -1093,7 +1093,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>36</v>
       </c>
@@ -1107,7 +1107,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>38</v>
       </c>
@@ -1121,7 +1121,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>40</v>
       </c>
@@ -1135,7 +1135,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>42</v>
       </c>
@@ -1152,7 +1152,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>44</v>
       </c>
@@ -1172,7 +1172,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>46</v>
       </c>
@@ -1186,7 +1186,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>46</v>
       </c>
@@ -1203,7 +1203,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>49</v>
       </c>
@@ -1217,7 +1217,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>51</v>
       </c>
@@ -1231,7 +1231,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>53</v>
       </c>
@@ -1245,7 +1245,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>55</v>
       </c>
@@ -1262,7 +1262,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>55</v>
       </c>
@@ -1282,7 +1282,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>58</v>
       </c>
@@ -1296,7 +1296,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>58</v>
       </c>
@@ -1316,7 +1316,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>61</v>
       </c>
@@ -1333,7 +1333,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>63</v>
       </c>
@@ -1347,7 +1347,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>65</v>
       </c>
@@ -1361,7 +1361,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>67</v>
       </c>
@@ -1375,7 +1375,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>69</v>
       </c>
@@ -1389,7 +1389,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>71</v>
       </c>
@@ -1403,7 +1403,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>73</v>
       </c>
@@ -1417,7 +1417,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>75</v>
       </c>
@@ -1431,7 +1431,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>77</v>
       </c>
@@ -1445,7 +1445,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>79</v>
       </c>
@@ -1459,7 +1459,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>81</v>
       </c>
@@ -1476,7 +1476,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>83</v>
       </c>
@@ -1496,7 +1496,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>85</v>
       </c>
@@ -1510,7 +1510,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>87</v>
       </c>
@@ -1524,7 +1524,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>89</v>
       </c>
@@ -1541,7 +1541,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>91</v>
       </c>
@@ -1555,7 +1555,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>93</v>
       </c>
@@ -1569,7 +1569,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>95</v>
       </c>
@@ -1583,7 +1583,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>95</v>
       </c>
@@ -1597,7 +1597,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>98</v>
       </c>
@@ -1611,7 +1611,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>98</v>
       </c>
@@ -1625,7 +1625,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>101</v>
       </c>
@@ -1639,7 +1639,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>101</v>
       </c>
@@ -1653,7 +1653,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>104</v>
       </c>
@@ -1667,7 +1667,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>104</v>
       </c>
@@ -1681,7 +1681,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>6</v>
       </c>
@@ -1698,7 +1698,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>108</v>
       </c>
@@ -1712,7 +1712,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>10</v>
       </c>
@@ -1729,7 +1729,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>12</v>
       </c>
@@ -1746,7 +1746,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>17</v>
       </c>
@@ -1766,7 +1766,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>19</v>
       </c>
@@ -1786,7 +1786,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>110</v>
       </c>
@@ -1800,7 +1800,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>21</v>
       </c>
@@ -1817,7 +1817,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>21</v>
       </c>
@@ -1831,7 +1831,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>25</v>
       </c>
@@ -1848,7 +1848,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>25</v>
       </c>
@@ -1862,7 +1862,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>28</v>
       </c>
@@ -1879,7 +1879,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>30</v>
       </c>
@@ -1893,7 +1893,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>36</v>
       </c>
@@ -1907,7 +1907,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>38</v>
       </c>
@@ -1921,7 +1921,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>112</v>
       </c>
@@ -1938,7 +1938,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>114</v>
       </c>
@@ -1958,7 +1958,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>42</v>
       </c>
@@ -1978,7 +1978,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>44</v>
       </c>
@@ -1998,7 +1998,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>116</v>
       </c>
@@ -2015,7 +2015,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>118</v>
       </c>
@@ -2029,7 +2029,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>120</v>
       </c>
@@ -2046,7 +2046,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>122</v>
       </c>
@@ -2063,7 +2063,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>53</v>
       </c>
@@ -2077,7 +2077,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>55</v>
       </c>
@@ -2094,7 +2094,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>55</v>
       </c>
@@ -2114,7 +2114,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>58</v>
       </c>
@@ -2128,7 +2128,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>58</v>
       </c>
@@ -2145,7 +2145,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>125</v>
       </c>
@@ -2162,7 +2162,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>127</v>
       </c>
@@ -2176,7 +2176,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>129</v>
       </c>
@@ -2190,7 +2190,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>131</v>
       </c>
@@ -2204,7 +2204,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>133</v>
       </c>
@@ -2218,7 +2218,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>135</v>
       </c>
@@ -2235,7 +2235,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>61</v>
       </c>
@@ -2255,7 +2255,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>63</v>
       </c>
@@ -2269,7 +2269,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>67</v>
       </c>
@@ -2283,7 +2283,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>69</v>
       </c>
@@ -2297,7 +2297,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>71</v>
       </c>
@@ -2314,7 +2314,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>73</v>
       </c>
@@ -2331,7 +2331,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>75</v>
       </c>
@@ -2351,7 +2351,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>77</v>
       </c>
@@ -2365,7 +2365,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>79</v>
       </c>
@@ -2379,7 +2379,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>137</v>
       </c>
@@ -2393,7 +2393,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>139</v>
       </c>
@@ -2413,7 +2413,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>141</v>
       </c>
@@ -2430,7 +2430,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>143</v>
       </c>
@@ -2444,7 +2444,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>145</v>
       </c>
@@ -2464,7 +2464,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>147</v>
       </c>
@@ -2481,7 +2481,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>89</v>
       </c>
@@ -2498,7 +2498,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>91</v>
       </c>
@@ -2512,7 +2512,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>93</v>
       </c>
@@ -2526,7 +2526,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>149</v>
       </c>
@@ -2540,7 +2540,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>151</v>
       </c>
@@ -2557,7 +2557,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>153</v>
       </c>
@@ -2571,7 +2571,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>155</v>
       </c>
@@ -2585,7 +2585,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>157</v>
       </c>

--- a/html/Sygehus-EPJ-systemer_excel.XLSX
+++ b/html/Sygehus-EPJ-systemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A016F9C-07C1-4B3D-BCA7-55912B3031F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96CFB54C-8F88-4949-A02D-E3F4DA651D48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4560" yWindow="945" windowWidth="21600" windowHeight="12450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 21-08-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 27-08-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sygehus_EPJ_systemer">'Opdateret d. 21-08-2026'!$A$1:$F$111</definedName>
+    <definedName name="Sygehus_EPJ_systemer">'Opdateret d. 27-08-2026'!$A$1:$F$111</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -842,9 +842,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F111"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -864,7 +864,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -881,7 +881,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -895,7 +895,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -912,7 +912,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -932,7 +932,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>17</v>
       </c>
@@ -952,7 +952,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>19</v>
       </c>
@@ -972,7 +972,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>21</v>
       </c>
@@ -989,7 +989,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>21</v>
       </c>
@@ -1003,7 +1003,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>25</v>
       </c>
@@ -1020,7 +1020,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>25</v>
       </c>
@@ -1034,7 +1034,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>28</v>
       </c>
@@ -1051,7 +1051,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>30</v>
       </c>
@@ -1065,7 +1065,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>32</v>
       </c>
@@ -1079,7 +1079,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>34</v>
       </c>
@@ -1093,7 +1093,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>36</v>
       </c>
@@ -1107,7 +1107,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>38</v>
       </c>
@@ -1121,7 +1121,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>40</v>
       </c>
@@ -1135,7 +1135,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>42</v>
       </c>
@@ -1152,7 +1152,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>44</v>
       </c>
@@ -1172,7 +1172,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>46</v>
       </c>
@@ -1186,7 +1186,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>46</v>
       </c>
@@ -1203,7 +1203,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>49</v>
       </c>
@@ -1217,7 +1217,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>51</v>
       </c>
@@ -1231,7 +1231,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>53</v>
       </c>
@@ -1245,7 +1245,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>55</v>
       </c>
@@ -1262,7 +1262,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>55</v>
       </c>
@@ -1282,7 +1282,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>58</v>
       </c>
@@ -1296,7 +1296,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>58</v>
       </c>
@@ -1316,7 +1316,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>61</v>
       </c>
@@ -1333,7 +1333,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>63</v>
       </c>
@@ -1347,7 +1347,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>65</v>
       </c>
@@ -1361,7 +1361,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>67</v>
       </c>
@@ -1375,7 +1375,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>69</v>
       </c>
@@ -1389,7 +1389,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>71</v>
       </c>
@@ -1403,7 +1403,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>73</v>
       </c>
@@ -1417,7 +1417,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>75</v>
       </c>
@@ -1431,7 +1431,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>77</v>
       </c>
@@ -1445,7 +1445,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>79</v>
       </c>
@@ -1459,7 +1459,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>81</v>
       </c>
@@ -1476,7 +1476,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>83</v>
       </c>
@@ -1496,7 +1496,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>85</v>
       </c>
@@ -1510,7 +1510,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>87</v>
       </c>
@@ -1524,7 +1524,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>89</v>
       </c>
@@ -1541,7 +1541,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>91</v>
       </c>
@@ -1555,7 +1555,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>93</v>
       </c>
@@ -1569,7 +1569,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>95</v>
       </c>
@@ -1583,7 +1583,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>95</v>
       </c>
@@ -1597,7 +1597,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>98</v>
       </c>
@@ -1611,7 +1611,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>98</v>
       </c>
@@ -1625,7 +1625,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>101</v>
       </c>
@@ -1639,7 +1639,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>101</v>
       </c>
@@ -1653,7 +1653,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>104</v>
       </c>
@@ -1667,7 +1667,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>104</v>
       </c>
@@ -1681,7 +1681,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>6</v>
       </c>
@@ -1698,7 +1698,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>108</v>
       </c>
@@ -1712,7 +1712,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>10</v>
       </c>
@@ -1729,7 +1729,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>12</v>
       </c>
@@ -1746,7 +1746,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>17</v>
       </c>
@@ -1766,7 +1766,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>19</v>
       </c>
@@ -1786,7 +1786,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>110</v>
       </c>
@@ -1800,7 +1800,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>21</v>
       </c>
@@ -1817,7 +1817,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>21</v>
       </c>
@@ -1831,7 +1831,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>25</v>
       </c>
@@ -1848,7 +1848,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>25</v>
       </c>
@@ -1862,7 +1862,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>28</v>
       </c>
@@ -1879,7 +1879,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>30</v>
       </c>
@@ -1893,7 +1893,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>36</v>
       </c>
@@ -1907,7 +1907,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>38</v>
       </c>
@@ -1921,7 +1921,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>112</v>
       </c>
@@ -1938,7 +1938,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>114</v>
       </c>
@@ -1958,7 +1958,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>42</v>
       </c>
@@ -1978,7 +1978,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>44</v>
       </c>
@@ -1998,7 +1998,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>116</v>
       </c>
@@ -2015,7 +2015,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>118</v>
       </c>
@@ -2029,7 +2029,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>120</v>
       </c>
@@ -2046,7 +2046,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>122</v>
       </c>
@@ -2063,7 +2063,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>53</v>
       </c>
@@ -2077,7 +2077,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>55</v>
       </c>
@@ -2094,7 +2094,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>55</v>
       </c>
@@ -2114,7 +2114,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>58</v>
       </c>
@@ -2128,7 +2128,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>58</v>
       </c>
@@ -2145,7 +2145,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>125</v>
       </c>
@@ -2162,7 +2162,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>127</v>
       </c>
@@ -2176,7 +2176,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>129</v>
       </c>
@@ -2190,7 +2190,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>131</v>
       </c>
@@ -2204,7 +2204,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>133</v>
       </c>
@@ -2218,7 +2218,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>135</v>
       </c>
@@ -2235,7 +2235,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>61</v>
       </c>
@@ -2255,7 +2255,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>63</v>
       </c>
@@ -2269,7 +2269,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>67</v>
       </c>
@@ -2283,7 +2283,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>69</v>
       </c>
@@ -2297,7 +2297,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>71</v>
       </c>
@@ -2314,7 +2314,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>73</v>
       </c>
@@ -2331,7 +2331,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>75</v>
       </c>
@@ -2351,7 +2351,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>77</v>
       </c>
@@ -2365,7 +2365,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>79</v>
       </c>
@@ -2379,7 +2379,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>137</v>
       </c>
@@ -2393,7 +2393,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>139</v>
       </c>
@@ -2413,7 +2413,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>141</v>
       </c>
@@ -2430,7 +2430,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>143</v>
       </c>
@@ -2444,7 +2444,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>145</v>
       </c>
@@ -2464,7 +2464,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>147</v>
       </c>
@@ -2481,7 +2481,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>89</v>
       </c>
@@ -2498,7 +2498,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>91</v>
       </c>
@@ -2512,7 +2512,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>93</v>
       </c>
@@ -2526,7 +2526,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>149</v>
       </c>
@@ -2540,7 +2540,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>151</v>
       </c>
@@ -2557,7 +2557,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>153</v>
       </c>
@@ -2571,7 +2571,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>155</v>
       </c>
@@ -2585,7 +2585,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>157</v>
       </c>

--- a/html/Sygehus-EPJ-systemer_excel.XLSX
+++ b/html/Sygehus-EPJ-systemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96CFB54C-8F88-4949-A02D-E3F4DA651D48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73AD830D-7FC1-4CDC-B357-A11D7A862B2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 27-08-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 02-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sygehus_EPJ_systemer">'Opdateret d. 27-08-2026'!$A$1:$F$111</definedName>
+    <definedName name="Sygehus_EPJ_systemer">'Opdateret d. 02-09-2026'!$A$1:$F$111</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Sygehus-EPJ-systemer_excel.XLSX
+++ b/html/Sygehus-EPJ-systemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73AD830D-7FC1-4CDC-B357-A11D7A862B2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A363CE60-289B-4118-9010-5A34B14A62EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14625" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 02-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 06-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sygehus_EPJ_systemer">'Opdateret d. 02-09-2026'!$A$1:$F$111</definedName>
+    <definedName name="Sygehus_EPJ_systemer">'Opdateret d. 06-09-2026'!$A$1:$F$111</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Sygehus-EPJ-systemer_excel.XLSX
+++ b/html/Sygehus-EPJ-systemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A363CE60-289B-4118-9010-5A34B14A62EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EE6D006-0072-4A1F-8BFC-FF471009CFAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14625" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Sygehus-EPJ-systemer_excel.XLSX
+++ b/html/Sygehus-EPJ-systemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EE6D006-0072-4A1F-8BFC-FF471009CFAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4C33E1C-DA6A-46CA-8D32-9C5C556A68BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14625" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 06-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 07-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sygehus_EPJ_systemer">'Opdateret d. 06-09-2026'!$A$1:$F$111</definedName>
+    <definedName name="Sygehus_EPJ_systemer">'Opdateret d. 07-09-2026'!$A$1:$F$111</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Sygehus-EPJ-systemer_excel.XLSX
+++ b/html/Sygehus-EPJ-systemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4C33E1C-DA6A-46CA-8D32-9C5C556A68BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2E8086E-2873-4C31-9C21-E282B8C5FBCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 07-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 09-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sygehus_EPJ_systemer">'Opdateret d. 07-09-2026'!$A$1:$F$111</definedName>
+    <definedName name="Sygehus_EPJ_systemer">'Opdateret d. 09-09-2026'!$A$1:$F$111</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Sygehus-EPJ-systemer_excel.XLSX
+++ b/html/Sygehus-EPJ-systemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2E8086E-2873-4C31-9C21-E282B8C5FBCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F576DE58-0242-422D-9C8F-DC9918327408}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
